--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannbn/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353E6C2C-A9B4-284F-A7F6-EC1A23886191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EB3EEE-DEB5-E34A-A369-E20FFD3D55AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="877" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2264,7 +2264,7 @@
     <numFmt numFmtId="168" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2386,12 +2386,6 @@
       <sz val="10"/>
       <color rgb="FF383A42"/>
       <name val="Menlo"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2960,36 +2954,22 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2997,12 +2977,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3018,6 +2999,19 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3049,14 +3043,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3070,73 +3059,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3198,6 +3121,98 @@
       </font>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
@@ -3226,109 +3241,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -3337,70 +3249,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3487,6 +3335,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -3494,7 +3356,45 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3548,9 +3448,84 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3567,9 +3542,28 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3644,6 +3638,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -3659,6 +3660,34 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3693,7 +3722,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3707,42 +3736,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3761,14 +3755,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3793,7 +3787,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3807,7 +3801,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3849,7 +3843,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3863,7 +3857,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3879,7 +3873,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3893,7 +3887,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3915,32 +3909,6 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3978,7 +3946,33 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3992,7 +3986,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4034,13 +4028,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4049,6 +4036,13 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4113,7 +4107,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4127,7 +4121,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4139,7 +4133,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4153,7 +4147,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4178,16 +4172,155 @@
     <dxf>
       <font>
         <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <i/>
       </font>
       <fill>
         <patternFill patternType="gray0625"/>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -4225,59 +4358,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4298,6 +4379,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -4305,7 +4393,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4319,101 +4407,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4467,7 +4461,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4481,14 +4475,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4502,7 +4496,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4527,60 +4521,6 @@
       </font>
       <fill>
         <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -4628,6 +4568,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -4636,6 +4583,53 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4663,14 +4657,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4837,21 +4831,16 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4885,6 +4874,11 @@
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4941,7 +4935,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4955,14 +4949,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4974,14 +4963,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5003,16 +4992,21 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5034,14 +5028,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5606,10 +5600,10 @@
       <c r="S3" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="147" t="s">
+      <c r="T3" s="145" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="154" t="s">
+      <c r="U3" s="148" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="49"/>
@@ -5705,8 +5699,8 @@
       <c r="S4" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="149"/>
-      <c r="U4" s="149"/>
+      <c r="T4" s="143"/>
+      <c r="U4" s="143"/>
       <c r="V4" s="49"/>
       <c r="W4" s="77" t="s">
         <v>43</v>
@@ -5797,7 +5791,7 @@
       <c r="T5" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="154" t="s">
+      <c r="U5" s="148" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="49"/>
@@ -5889,7 +5883,7 @@
       <c r="T6" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="U6" s="149"/>
+      <c r="U6" s="143"/>
       <c r="V6" s="49"/>
       <c r="W6" s="77" t="s">
         <v>43</v>
@@ -6231,13 +6225,13 @@
       <c r="R11" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="147" t="s">
+      <c r="S11" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="147" t="s">
+      <c r="T11" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="152" t="s">
+      <c r="U11" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="49"/>
@@ -6330,9 +6324,9 @@
       <c r="R12" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="S12" s="148"/>
-      <c r="T12" s="148"/>
-      <c r="U12" s="148"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="142"/>
+      <c r="U12" s="142"/>
       <c r="V12" s="49"/>
       <c r="W12" s="77" t="s">
         <v>77</v>
@@ -6423,9 +6417,9 @@
       <c r="R13" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="S13" s="149"/>
-      <c r="T13" s="149"/>
-      <c r="U13" s="149"/>
+      <c r="S13" s="143"/>
+      <c r="T13" s="143"/>
+      <c r="U13" s="143"/>
       <c r="V13" s="49"/>
       <c r="W13" s="77" t="s">
         <v>77</v>
@@ -6554,13 +6548,13 @@
       <c r="R15" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S15" s="147" t="s">
+      <c r="S15" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T15" s="147" t="s">
+      <c r="T15" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U15" s="152" t="s">
+      <c r="U15" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V15" s="49"/>
@@ -6646,9 +6640,9 @@
       <c r="R16" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S16" s="148"/>
-      <c r="T16" s="148"/>
-      <c r="U16" s="148"/>
+      <c r="S16" s="142"/>
+      <c r="T16" s="142"/>
+      <c r="U16" s="142"/>
       <c r="V16" s="49"/>
       <c r="W16" s="77" t="s">
         <v>77</v>
@@ -6732,9 +6726,9 @@
       <c r="R17" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S17" s="149"/>
-      <c r="T17" s="149"/>
-      <c r="U17" s="149"/>
+      <c r="S17" s="143"/>
+      <c r="T17" s="143"/>
+      <c r="U17" s="143"/>
       <c r="V17" s="49"/>
       <c r="W17" s="77" t="s">
         <v>77</v>
@@ -7100,13 +7094,13 @@
       <c r="R22" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S22" s="147" t="s">
+      <c r="S22" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T22" s="147" t="s">
+      <c r="T22" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U22" s="152" t="s">
+      <c r="U22" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V22" s="49"/>
@@ -7192,9 +7186,9 @@
       <c r="R23" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S23" s="148"/>
-      <c r="T23" s="148"/>
-      <c r="U23" s="148"/>
+      <c r="S23" s="142"/>
+      <c r="T23" s="142"/>
+      <c r="U23" s="142"/>
       <c r="V23" s="49"/>
       <c r="W23" s="77" t="s">
         <v>77</v>
@@ -7278,9 +7272,9 @@
       <c r="R24" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S24" s="149"/>
-      <c r="T24" s="149"/>
-      <c r="U24" s="149"/>
+      <c r="S24" s="143"/>
+      <c r="T24" s="143"/>
+      <c r="U24" s="143"/>
       <c r="V24" s="49"/>
       <c r="W24" s="77" t="s">
         <v>77</v>
@@ -7409,13 +7403,13 @@
       <c r="R26" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S26" s="147" t="s">
+      <c r="S26" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T26" s="147" t="s">
+      <c r="T26" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U26" s="152" t="s">
+      <c r="U26" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V26" s="49"/>
@@ -7501,9 +7495,9 @@
       <c r="R27" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S27" s="148"/>
-      <c r="T27" s="148"/>
-      <c r="U27" s="148"/>
+      <c r="S27" s="142"/>
+      <c r="T27" s="142"/>
+      <c r="U27" s="142"/>
       <c r="V27" s="49"/>
       <c r="W27" s="77" t="s">
         <v>77</v>
@@ -7587,9 +7581,9 @@
       <c r="R28" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S28" s="149"/>
-      <c r="T28" s="149"/>
-      <c r="U28" s="149"/>
+      <c r="S28" s="143"/>
+      <c r="T28" s="143"/>
+      <c r="U28" s="143"/>
       <c r="V28" s="49"/>
       <c r="W28" s="77" t="s">
         <v>77</v>
@@ -7726,13 +7720,13 @@
       <c r="R30" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S30" s="147" t="s">
+      <c r="S30" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T30" s="147" t="s">
+      <c r="T30" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U30" s="152" t="s">
+      <c r="U30" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V30" s="49"/>
@@ -7822,9 +7816,9 @@
       <c r="R31" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S31" s="148"/>
-      <c r="T31" s="148"/>
-      <c r="U31" s="148"/>
+      <c r="S31" s="142"/>
+      <c r="T31" s="142"/>
+      <c r="U31" s="142"/>
       <c r="V31" s="49"/>
       <c r="W31" s="77" t="s">
         <v>77</v>
@@ -7912,9 +7906,9 @@
       <c r="R32" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S32" s="149"/>
-      <c r="T32" s="149"/>
-      <c r="U32" s="149"/>
+      <c r="S32" s="143"/>
+      <c r="T32" s="143"/>
+      <c r="U32" s="143"/>
       <c r="V32" s="49"/>
       <c r="W32" s="77" t="s">
         <v>77</v>
@@ -8233,13 +8227,13 @@
       <c r="R37" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S37" s="147" t="s">
+      <c r="S37" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T37" s="147" t="s">
+      <c r="T37" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U37" s="152" t="s">
+      <c r="U37" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V37" s="49"/>
@@ -8323,9 +8317,9 @@
       <c r="R38" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S38" s="148"/>
-      <c r="T38" s="148"/>
-      <c r="U38" s="148"/>
+      <c r="S38" s="142"/>
+      <c r="T38" s="142"/>
+      <c r="U38" s="142"/>
       <c r="V38" s="49"/>
       <c r="W38" s="77" t="s">
         <v>77</v>
@@ -8409,9 +8403,9 @@
       <c r="R39" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S39" s="149"/>
-      <c r="T39" s="149"/>
-      <c r="U39" s="149"/>
+      <c r="S39" s="143"/>
+      <c r="T39" s="143"/>
+      <c r="U39" s="143"/>
       <c r="V39" s="49"/>
       <c r="W39" s="77" t="s">
         <v>77</v>
@@ -8540,13 +8534,13 @@
       <c r="R41" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S41" s="147" t="s">
+      <c r="S41" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="147" t="s">
+      <c r="T41" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U41" s="152" t="s">
+      <c r="U41" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V41" s="49"/>
@@ -8632,9 +8626,9 @@
       <c r="R42" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S42" s="148"/>
-      <c r="T42" s="148"/>
-      <c r="U42" s="148"/>
+      <c r="S42" s="142"/>
+      <c r="T42" s="142"/>
+      <c r="U42" s="142"/>
       <c r="V42" s="49"/>
       <c r="W42" s="77" t="s">
         <v>77</v>
@@ -8718,9 +8712,9 @@
       <c r="R43" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S43" s="149"/>
-      <c r="T43" s="149"/>
-      <c r="U43" s="149"/>
+      <c r="S43" s="143"/>
+      <c r="T43" s="143"/>
+      <c r="U43" s="143"/>
       <c r="V43" s="49"/>
       <c r="W43" s="77" t="s">
         <v>77</v>
@@ -8901,13 +8895,13 @@
       <c r="R46" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S46" s="147" t="s">
+      <c r="S46" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T46" s="147" t="s">
+      <c r="T46" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U46" s="152" t="s">
+      <c r="U46" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V46" s="49"/>
@@ -8993,9 +8987,9 @@
       <c r="R47" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S47" s="148"/>
-      <c r="T47" s="148"/>
-      <c r="U47" s="148"/>
+      <c r="S47" s="142"/>
+      <c r="T47" s="142"/>
+      <c r="U47" s="142"/>
       <c r="V47" s="49"/>
       <c r="W47" s="77" t="s">
         <v>77</v>
@@ -9079,9 +9073,9 @@
       <c r="R48" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S48" s="149"/>
-      <c r="T48" s="149"/>
-      <c r="U48" s="149"/>
+      <c r="S48" s="143"/>
+      <c r="T48" s="143"/>
+      <c r="U48" s="143"/>
       <c r="V48" s="49"/>
       <c r="W48" s="77" t="s">
         <v>77</v>
@@ -9352,16 +9346,16 @@
       <c r="R52" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S52" s="147" t="s">
+      <c r="S52" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T52" s="147" t="s">
+      <c r="T52" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="152" t="s">
+      <c r="U52" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="V52" s="153" t="s">
+      <c r="V52" s="150" t="s">
         <v>162</v>
       </c>
       <c r="W52" s="77" t="s">
@@ -9446,10 +9440,10 @@
       <c r="R53" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S53" s="148"/>
-      <c r="T53" s="148"/>
-      <c r="U53" s="148"/>
-      <c r="V53" s="148"/>
+      <c r="S53" s="142"/>
+      <c r="T53" s="142"/>
+      <c r="U53" s="142"/>
+      <c r="V53" s="142"/>
       <c r="W53" s="77" t="s">
         <v>77</v>
       </c>
@@ -9532,10 +9526,10 @@
       <c r="R54" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S54" s="149"/>
-      <c r="T54" s="149"/>
-      <c r="U54" s="149"/>
-      <c r="V54" s="149"/>
+      <c r="S54" s="143"/>
+      <c r="T54" s="143"/>
+      <c r="U54" s="143"/>
+      <c r="V54" s="143"/>
       <c r="W54" s="77" t="s">
         <v>77</v>
       </c>
@@ -9708,13 +9702,13 @@
       <c r="R57" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S57" s="147" t="s">
+      <c r="S57" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T57" s="147" t="s">
+      <c r="T57" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="152" t="s">
+      <c r="U57" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="49"/>
@@ -9800,9 +9794,9 @@
       <c r="R58" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S58" s="148"/>
-      <c r="T58" s="148"/>
-      <c r="U58" s="148"/>
+      <c r="S58" s="142"/>
+      <c r="T58" s="142"/>
+      <c r="U58" s="142"/>
       <c r="V58" s="49"/>
       <c r="W58" s="77" t="s">
         <v>77</v>
@@ -9886,9 +9880,9 @@
       <c r="R59" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S59" s="149"/>
-      <c r="T59" s="149"/>
-      <c r="U59" s="149"/>
+      <c r="S59" s="143"/>
+      <c r="T59" s="143"/>
+      <c r="U59" s="143"/>
       <c r="V59" s="49"/>
       <c r="W59" s="77" t="s">
         <v>77</v>
@@ -10017,13 +10011,13 @@
       <c r="R61" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S61" s="147" t="s">
+      <c r="S61" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T61" s="147" t="s">
+      <c r="T61" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U61" s="152" t="s">
+      <c r="U61" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V61" s="49"/>
@@ -10109,9 +10103,9 @@
       <c r="R62" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S62" s="148"/>
-      <c r="T62" s="148"/>
-      <c r="U62" s="148"/>
+      <c r="S62" s="142"/>
+      <c r="T62" s="142"/>
+      <c r="U62" s="142"/>
       <c r="V62" s="49"/>
       <c r="W62" s="77" t="s">
         <v>77</v>
@@ -10195,9 +10189,9 @@
       <c r="R63" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S63" s="149"/>
-      <c r="T63" s="149"/>
-      <c r="U63" s="149"/>
+      <c r="S63" s="143"/>
+      <c r="T63" s="143"/>
+      <c r="U63" s="143"/>
       <c r="V63" s="49"/>
       <c r="W63" s="77" t="s">
         <v>77</v>
@@ -10521,7 +10515,7 @@
       <c r="S68" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T68" s="150" t="s">
+      <c r="T68" s="146" t="s">
         <v>197</v>
       </c>
       <c r="U68" s="56"/>
@@ -10612,7 +10606,7 @@
       <c r="S69" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T69" s="148"/>
+      <c r="T69" s="142"/>
       <c r="U69" s="56"/>
       <c r="V69" s="49"/>
       <c r="W69" s="77" t="s">
@@ -10708,7 +10702,7 @@
       <c r="S70" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T70" s="148"/>
+      <c r="T70" s="142"/>
       <c r="U70" s="56"/>
       <c r="V70" s="49"/>
       <c r="W70" s="77" t="s">
@@ -10811,7 +10805,7 @@
       <c r="S71" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T71" s="148"/>
+      <c r="T71" s="142"/>
       <c r="U71" s="56"/>
       <c r="V71" s="59" t="s">
         <v>203</v>
@@ -10909,7 +10903,7 @@
       <c r="S72" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T72" s="148"/>
+      <c r="T72" s="142"/>
       <c r="U72" s="56"/>
       <c r="V72" s="59"/>
       <c r="W72" s="77" t="s">
@@ -11005,7 +10999,7 @@
       <c r="S73" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T73" s="149"/>
+      <c r="T73" s="143"/>
       <c r="U73" s="56"/>
       <c r="V73" s="59"/>
       <c r="W73" s="77" t="s">
@@ -11202,10 +11196,10 @@
       <c r="S76" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="T76" s="150" t="s">
+      <c r="T76" s="146" t="s">
         <v>210</v>
       </c>
-      <c r="U76" s="156" t="s">
+      <c r="U76" s="147" t="s">
         <v>211</v>
       </c>
       <c r="V76" s="59" t="s">
@@ -11301,8 +11295,8 @@
       <c r="S77" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="T77" s="148"/>
-      <c r="U77" s="148"/>
+      <c r="T77" s="142"/>
+      <c r="U77" s="142"/>
       <c r="V77" s="49"/>
       <c r="W77" s="77" t="s">
         <v>213</v>
@@ -11405,8 +11399,8 @@
       <c r="S78" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="T78" s="148"/>
-      <c r="U78" s="148"/>
+      <c r="T78" s="142"/>
+      <c r="U78" s="142"/>
       <c r="V78" s="49"/>
       <c r="W78" s="77" t="s">
         <v>157</v>
@@ -11501,8 +11495,8 @@
       <c r="S79" s="59" t="s">
         <v>221</v>
       </c>
-      <c r="T79" s="148"/>
-      <c r="U79" s="148"/>
+      <c r="T79" s="142"/>
+      <c r="U79" s="142"/>
       <c r="V79" s="49"/>
       <c r="W79" s="77" t="s">
         <v>157</v>
@@ -11605,8 +11599,8 @@
       <c r="S80" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="T80" s="149"/>
-      <c r="U80" s="149"/>
+      <c r="T80" s="143"/>
+      <c r="U80" s="143"/>
       <c r="V80" s="49"/>
       <c r="W80" s="77" t="s">
         <v>226</v>
@@ -12120,7 +12114,7 @@
       <c r="T86" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="U86" s="156" t="s">
+      <c r="U86" s="147" t="s">
         <v>211</v>
       </c>
       <c r="V86" s="49"/>
@@ -12228,7 +12222,7 @@
       <c r="T87" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="U87" s="148"/>
+      <c r="U87" s="142"/>
       <c r="V87" s="49"/>
       <c r="W87" s="77" t="s">
         <v>226</v>
@@ -12327,7 +12321,7 @@
       <c r="T88" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="U88" s="148"/>
+      <c r="U88" s="142"/>
       <c r="V88" s="49"/>
       <c r="W88" s="77" t="s">
         <v>228</v>
@@ -12424,7 +12418,7 @@
       <c r="T89" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="U89" s="148"/>
+      <c r="U89" s="142"/>
       <c r="V89" s="49"/>
       <c r="W89" s="77" t="s">
         <v>228</v>
@@ -12515,7 +12509,7 @@
       <c r="T90" s="59" t="s">
         <v>231</v>
       </c>
-      <c r="U90" s="148"/>
+      <c r="U90" s="142"/>
       <c r="V90" s="49"/>
       <c r="W90" s="77" t="s">
         <v>157</v>
@@ -12606,7 +12600,7 @@
       <c r="T91" s="59" t="s">
         <v>231</v>
       </c>
-      <c r="U91" s="148"/>
+      <c r="U91" s="142"/>
       <c r="V91" s="49"/>
       <c r="W91" s="77" t="s">
         <v>157</v>
@@ -12695,7 +12689,7 @@
         <v>242</v>
       </c>
       <c r="T92" s="59"/>
-      <c r="U92" s="148"/>
+      <c r="U92" s="142"/>
       <c r="V92" s="49"/>
       <c r="W92" s="77" t="s">
         <v>157</v>
@@ -12784,7 +12778,7 @@
         <v>242</v>
       </c>
       <c r="T93" s="59"/>
-      <c r="U93" s="148"/>
+      <c r="U93" s="142"/>
       <c r="V93" s="49"/>
       <c r="W93" s="77" t="s">
         <v>157</v>
@@ -12862,7 +12856,7 @@
       <c r="R94" s="49"/>
       <c r="S94" s="59"/>
       <c r="T94" s="59"/>
-      <c r="U94" s="148"/>
+      <c r="U94" s="142"/>
       <c r="V94" s="49"/>
       <c r="W94" s="77"/>
       <c r="X94" s="80"/>
@@ -12943,7 +12937,7 @@
         <v>209</v>
       </c>
       <c r="T95" s="59"/>
-      <c r="U95" s="148"/>
+      <c r="U95" s="142"/>
       <c r="V95" s="49"/>
       <c r="W95" s="77" t="s">
         <v>157</v>
@@ -13046,7 +13040,7 @@
         <v>209</v>
       </c>
       <c r="T96" s="59"/>
-      <c r="U96" s="149"/>
+      <c r="U96" s="143"/>
       <c r="V96" s="49"/>
       <c r="W96" s="77" t="s">
         <v>157</v>
@@ -13852,13 +13846,13 @@
       <c r="S106" s="59" t="s">
         <v>270</v>
       </c>
-      <c r="T106" s="150" t="s">
+      <c r="T106" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="U106" s="155" t="s">
+      <c r="U106" s="149" t="s">
         <v>272</v>
       </c>
-      <c r="V106" s="150"/>
+      <c r="V106" s="146"/>
       <c r="W106" s="77" t="s">
         <v>157</v>
       </c>
@@ -13954,9 +13948,9 @@
       <c r="S107" s="59" t="s">
         <v>275</v>
       </c>
-      <c r="T107" s="149"/>
-      <c r="U107" s="149"/>
-      <c r="V107" s="149"/>
+      <c r="T107" s="143"/>
+      <c r="U107" s="143"/>
+      <c r="V107" s="143"/>
       <c r="W107" s="77" t="s">
         <v>157</v>
       </c>
@@ -15143,7 +15137,7 @@
         <v>294</v>
       </c>
       <c r="U120" s="83"/>
-      <c r="V120" s="150" t="s">
+      <c r="V120" s="146" t="s">
         <v>309</v>
       </c>
       <c r="W120" s="77" t="s">
@@ -15243,7 +15237,7 @@
         <v>294</v>
       </c>
       <c r="U121" s="83"/>
-      <c r="V121" s="149"/>
+      <c r="V121" s="143"/>
       <c r="W121" s="77" t="s">
         <v>157</v>
       </c>
@@ -16263,10 +16257,10 @@
       <c r="R135" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S135" s="151" t="s">
+      <c r="S135" s="141" t="s">
         <v>342</v>
       </c>
-      <c r="T135" s="151" t="s">
+      <c r="T135" s="141" t="s">
         <v>343</v>
       </c>
       <c r="U135" s="49"/>
@@ -16355,8 +16349,8 @@
       <c r="R136" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S136" s="148"/>
-      <c r="T136" s="148"/>
+      <c r="S136" s="142"/>
+      <c r="T136" s="142"/>
       <c r="U136" s="49"/>
       <c r="V136" s="49"/>
       <c r="W136" s="77" t="s">
@@ -16443,8 +16437,8 @@
       <c r="R137" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S137" s="148"/>
-      <c r="T137" s="148"/>
+      <c r="S137" s="142"/>
+      <c r="T137" s="142"/>
       <c r="U137" s="49"/>
       <c r="V137" s="49"/>
       <c r="W137" s="77" t="s">
@@ -16531,8 +16525,8 @@
       <c r="R138" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S138" s="148"/>
-      <c r="T138" s="148"/>
+      <c r="S138" s="142"/>
+      <c r="T138" s="142"/>
       <c r="U138" s="49"/>
       <c r="V138" s="49"/>
       <c r="W138" s="77" t="s">
@@ -16619,8 +16613,8 @@
       <c r="R139" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S139" s="148"/>
-      <c r="T139" s="148"/>
+      <c r="S139" s="142"/>
+      <c r="T139" s="142"/>
       <c r="U139" s="49"/>
       <c r="V139" s="49"/>
       <c r="W139" s="77" t="s">
@@ -16707,8 +16701,8 @@
       <c r="R140" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S140" s="149"/>
-      <c r="T140" s="149"/>
+      <c r="S140" s="143"/>
+      <c r="T140" s="143"/>
       <c r="U140" s="49"/>
       <c r="V140" s="49"/>
       <c r="W140" s="77" t="s">
@@ -16833,10 +16827,10 @@
       <c r="R142" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S142" s="150" t="s">
+      <c r="S142" s="146" t="s">
         <v>352</v>
       </c>
-      <c r="T142" s="150" t="s">
+      <c r="T142" s="146" t="s">
         <v>353</v>
       </c>
       <c r="U142" s="49"/>
@@ -16920,8 +16914,8 @@
       <c r="R143" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S143" s="148"/>
-      <c r="T143" s="148"/>
+      <c r="S143" s="142"/>
+      <c r="T143" s="142"/>
       <c r="U143" s="49"/>
       <c r="V143" s="49"/>
       <c r="W143" s="77" t="s">
@@ -17005,8 +16999,8 @@
       <c r="R144" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S144" s="148"/>
-      <c r="T144" s="148"/>
+      <c r="S144" s="142"/>
+      <c r="T144" s="142"/>
       <c r="U144" s="49"/>
       <c r="V144" s="49"/>
       <c r="W144" s="77" t="s">
@@ -17096,8 +17090,8 @@
       <c r="R145" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S145" s="148"/>
-      <c r="T145" s="148"/>
+      <c r="S145" s="142"/>
+      <c r="T145" s="142"/>
       <c r="U145" s="49"/>
       <c r="V145" s="49"/>
       <c r="W145" s="77" t="s">
@@ -17194,8 +17188,8 @@
       <c r="R146" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S146" s="148"/>
-      <c r="T146" s="148"/>
+      <c r="S146" s="142"/>
+      <c r="T146" s="142"/>
       <c r="U146" s="49"/>
       <c r="V146" s="49"/>
       <c r="W146" s="77" t="s">
@@ -17288,8 +17282,8 @@
       <c r="R147" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S147" s="149"/>
-      <c r="T147" s="149"/>
+      <c r="S147" s="143"/>
+      <c r="T147" s="143"/>
       <c r="U147" s="49"/>
       <c r="V147" s="49"/>
       <c r="W147" s="77" t="s">
@@ -17605,7 +17599,7 @@
       <c r="R152" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="S152" s="147" t="s">
+      <c r="S152" s="145" t="s">
         <v>318</v>
       </c>
       <c r="T152" s="46"/>
@@ -17687,7 +17681,7 @@
       <c r="R153" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="S153" s="148"/>
+      <c r="S153" s="142"/>
       <c r="T153" s="46"/>
       <c r="U153" s="46"/>
       <c r="V153" s="46"/>
@@ -17767,7 +17761,7 @@
       <c r="R154" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="S154" s="148"/>
+      <c r="S154" s="142"/>
       <c r="T154" s="49"/>
       <c r="U154" s="49"/>
       <c r="V154" s="49"/>
@@ -17847,7 +17841,7 @@
       <c r="R155" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="S155" s="149"/>
+      <c r="S155" s="143"/>
       <c r="T155" s="49"/>
       <c r="U155" s="49"/>
       <c r="V155" s="49"/>
@@ -18861,14 +18855,14 @@
       <c r="P170" s="49"/>
       <c r="Q170" s="66"/>
       <c r="R170" s="49"/>
-      <c r="S170" s="150" t="s">
+      <c r="S170" s="146" t="s">
         <v>401</v>
       </c>
-      <c r="T170" s="150" t="s">
+      <c r="T170" s="146" t="s">
         <v>401</v>
       </c>
       <c r="U170" s="49"/>
-      <c r="V170" s="150" t="s">
+      <c r="V170" s="146" t="s">
         <v>402</v>
       </c>
       <c r="W170" s="77"/>
@@ -18912,10 +18906,10 @@
       <c r="P171" s="49"/>
       <c r="Q171" s="66"/>
       <c r="R171" s="49"/>
-      <c r="S171" s="148"/>
-      <c r="T171" s="148"/>
+      <c r="S171" s="142"/>
+      <c r="T171" s="142"/>
       <c r="U171" s="49"/>
-      <c r="V171" s="148"/>
+      <c r="V171" s="142"/>
       <c r="W171" s="77"/>
       <c r="X171" s="80"/>
       <c r="Y171" s="80"/>
@@ -18957,10 +18951,10 @@
       <c r="P172" s="49"/>
       <c r="Q172" s="66"/>
       <c r="R172" s="49"/>
-      <c r="S172" s="148"/>
-      <c r="T172" s="148"/>
+      <c r="S172" s="142"/>
+      <c r="T172" s="142"/>
       <c r="U172" s="49"/>
-      <c r="V172" s="148"/>
+      <c r="V172" s="142"/>
       <c r="W172" s="77"/>
       <c r="X172" s="80"/>
       <c r="Y172" s="80"/>
@@ -19002,10 +18996,10 @@
       <c r="P173" s="49"/>
       <c r="Q173" s="66"/>
       <c r="R173" s="49"/>
-      <c r="S173" s="148"/>
-      <c r="T173" s="148"/>
+      <c r="S173" s="142"/>
+      <c r="T173" s="142"/>
       <c r="U173" s="49"/>
-      <c r="V173" s="148"/>
+      <c r="V173" s="142"/>
       <c r="W173" s="77"/>
       <c r="X173" s="80"/>
       <c r="Y173" s="80"/>
@@ -19047,10 +19041,10 @@
       <c r="P174" s="49"/>
       <c r="Q174" s="66"/>
       <c r="R174" s="49"/>
-      <c r="S174" s="148"/>
-      <c r="T174" s="148"/>
+      <c r="S174" s="142"/>
+      <c r="T174" s="142"/>
       <c r="U174" s="49"/>
-      <c r="V174" s="148"/>
+      <c r="V174" s="142"/>
       <c r="W174" s="77"/>
       <c r="X174" s="80"/>
       <c r="Y174" s="80"/>
@@ -19092,10 +19086,10 @@
       <c r="P175" s="49"/>
       <c r="Q175" s="66"/>
       <c r="R175" s="49"/>
-      <c r="S175" s="148"/>
-      <c r="T175" s="148"/>
+      <c r="S175" s="142"/>
+      <c r="T175" s="142"/>
       <c r="U175" s="49"/>
-      <c r="V175" s="148"/>
+      <c r="V175" s="142"/>
       <c r="W175" s="77"/>
       <c r="X175" s="80"/>
       <c r="Y175" s="80"/>
@@ -19137,10 +19131,10 @@
       <c r="P176" s="49"/>
       <c r="Q176" s="66"/>
       <c r="R176" s="49"/>
-      <c r="S176" s="149"/>
-      <c r="T176" s="149"/>
+      <c r="S176" s="143"/>
+      <c r="T176" s="143"/>
       <c r="U176" s="49"/>
-      <c r="V176" s="149"/>
+      <c r="V176" s="143"/>
       <c r="W176" s="77"/>
       <c r="X176" s="80"/>
       <c r="Y176" s="80"/>
@@ -19500,6 +19494,43 @@
   </sheetData>
   <autoFilter ref="A1:AB181" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="53">
+    <mergeCell ref="T26:T28"/>
+    <mergeCell ref="T41:T43"/>
+    <mergeCell ref="V106:V107"/>
+    <mergeCell ref="T61:T63"/>
+    <mergeCell ref="T76:T80"/>
+    <mergeCell ref="S135:S140"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="V170:V176"/>
+    <mergeCell ref="S30:S32"/>
+    <mergeCell ref="S15:S17"/>
+    <mergeCell ref="T37:T39"/>
+    <mergeCell ref="T46:T48"/>
+    <mergeCell ref="T22:T24"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="U26:U28"/>
+    <mergeCell ref="T52:T54"/>
+    <mergeCell ref="V120:V121"/>
+    <mergeCell ref="S152:S155"/>
+    <mergeCell ref="T142:T147"/>
+    <mergeCell ref="V52:V54"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="U106:U107"/>
+    <mergeCell ref="T68:T73"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S22:S24"/>
+    <mergeCell ref="U22:U24"/>
+    <mergeCell ref="T30:T32"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="U37:U39"/>
+    <mergeCell ref="T106:T107"/>
     <mergeCell ref="T135:T140"/>
     <mergeCell ref="U30:U32"/>
     <mergeCell ref="S52:S54"/>
@@ -19516,53 +19547,16 @@
     <mergeCell ref="S57:S59"/>
     <mergeCell ref="S37:S39"/>
     <mergeCell ref="U86:U96"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T15:T17"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="U106:U107"/>
-    <mergeCell ref="T68:T73"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S22:S24"/>
-    <mergeCell ref="U22:U24"/>
-    <mergeCell ref="T30:T32"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="U37:U39"/>
-    <mergeCell ref="T106:T107"/>
-    <mergeCell ref="S135:S140"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="V170:V176"/>
-    <mergeCell ref="S30:S32"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="T37:T39"/>
-    <mergeCell ref="T46:T48"/>
-    <mergeCell ref="T22:T24"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="U26:U28"/>
-    <mergeCell ref="T52:T54"/>
-    <mergeCell ref="V120:V121"/>
-    <mergeCell ref="S152:S155"/>
-    <mergeCell ref="T142:T147"/>
-    <mergeCell ref="V52:V54"/>
-    <mergeCell ref="T26:T28"/>
-    <mergeCell ref="T41:T43"/>
-    <mergeCell ref="V106:V107"/>
-    <mergeCell ref="T61:T63"/>
-    <mergeCell ref="T76:T80"/>
   </mergeCells>
   <conditionalFormatting sqref="A97:B103">
     <cfRule type="expression" dxfId="298" priority="547">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="297" priority="548">
+    <cfRule type="expression" dxfId="297" priority="549">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="296" priority="548">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="296" priority="549">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106:F108 U113:V119 U120:U121 A135:B140 N142:V142 N143:R143 U143:V148 K144:R144 A148:T148 T152:V157 A158:V161 A162:J163">
@@ -19581,17 +19575,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A150:R157">
-    <cfRule type="expression" dxfId="292" priority="656">
+    <cfRule type="expression" dxfId="292" priority="657">
+      <formula>$B150=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="291" priority="656">
       <formula>$B150=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="291" priority="657">
-      <formula>$B150=2</formula>
+    <cfRule type="expression" dxfId="290" priority="659">
+      <formula>$B150=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="290" priority="658">
+    <cfRule type="expression" dxfId="289" priority="658">
       <formula>$B150&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="289" priority="659">
-      <formula>$B150=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A124:S125 U124:V125 U166:V168">
@@ -19600,28 +19594,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:U105">
-    <cfRule type="expression" dxfId="287" priority="764">
-      <formula>$B105=3</formula>
+    <cfRule type="expression" dxfId="287" priority="767">
+      <formula>$B105=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="286" priority="765">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="285" priority="766">
+    <cfRule type="expression" dxfId="285" priority="764">
+      <formula>$B105=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="284" priority="766">
       <formula>$B105&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="284" priority="767">
-      <formula>$B105=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74:V96 A104:V104 A170:R176">
-    <cfRule type="expression" dxfId="283" priority="461">
-      <formula>$B74=3</formula>
+    <cfRule type="expression" dxfId="283" priority="463">
+      <formula>$B74&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="282" priority="462">
       <formula>$B74=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="281" priority="463">
-      <formula>$B74&lt;2</formula>
+    <cfRule type="expression" dxfId="281" priority="461">
+      <formula>$B74=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:V83">
@@ -19661,33 +19655,33 @@
     <cfRule type="expression" dxfId="273" priority="693">
       <formula>$B149=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="272" priority="694">
+    <cfRule type="expression" dxfId="272" priority="695">
+      <formula>$B149=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="271" priority="694">
       <formula>$B149&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="271" priority="695">
-      <formula>$B149=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178:V181">
-    <cfRule type="expression" dxfId="270" priority="624">
+    <cfRule type="expression" dxfId="270" priority="627">
+      <formula>$B178=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="269" priority="624">
       <formula>$B178=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="269" priority="625">
+    <cfRule type="expression" dxfId="268" priority="625">
       <formula>$B178=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="268" priority="626">
+    <cfRule type="expression" dxfId="267" priority="626">
       <formula>$B178&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="267" priority="627">
-      <formula>$B178=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A106:F108 A109:V111 U113:V119 U120:U121 A124:S125 U124:V125 A135:B140 U135:V140 A141:V141 N142:V142 N143:R143 U143:V148 K144:R144 A148:T148 T152:V157 A158:V161 A162:J163 A164:L168 U166:V168">
-    <cfRule type="expression" dxfId="266" priority="761">
+    <cfRule type="expression" dxfId="266" priority="762">
+      <formula>$B1&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="265" priority="761">
       <formula>$B1=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="265" priority="762">
-      <formula>$B1&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG51 A170:R176">
@@ -19789,11 +19783,11 @@
     <cfRule type="expression" dxfId="241" priority="394">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="240" priority="395">
+    <cfRule type="expression" dxfId="240" priority="396">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="239" priority="395">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="239" priority="396">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99:C102">
@@ -19808,39 +19802,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101:C103">
-    <cfRule type="expression" dxfId="235" priority="380">
-      <formula>$B101=3</formula>
+    <cfRule type="expression" dxfId="235" priority="382">
+      <formula>$B101&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="234" priority="381">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="233" priority="382">
-      <formula>$B101&lt;2</formula>
+    <cfRule type="expression" dxfId="233" priority="380">
+      <formula>$B101=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102:C103">
     <cfRule type="expression" dxfId="232" priority="26">
       <formula>$B102=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="231" priority="27">
+    <cfRule type="expression" dxfId="231" priority="28">
+      <formula>$B102&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="230" priority="27">
       <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="230" priority="28">
-      <formula>$B102&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C135:T135 C136:R140">
-    <cfRule type="expression" dxfId="229" priority="583">
+    <cfRule type="expression" dxfId="229" priority="586">
+      <formula>$B135=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="228" priority="583">
       <formula>$B135=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="228" priority="584">
+    <cfRule type="expression" dxfId="227" priority="584">
       <formula>$B135=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="227" priority="585">
+    <cfRule type="expression" dxfId="226" priority="585">
       <formula>$B135&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="226" priority="586">
-      <formula>$B135=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D80 D82 D84:D134 D141:D181">
@@ -19884,25 +19878,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D97:E103">
-    <cfRule type="expression" dxfId="225" priority="373">
+    <cfRule type="expression" dxfId="225" priority="375">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="224" priority="373">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="224" priority="374">
+    <cfRule type="expression" dxfId="223" priority="374">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="223" priority="375">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E97:E103">
-    <cfRule type="expression" dxfId="222" priority="370">
+    <cfRule type="expression" dxfId="222" priority="372">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="221" priority="370">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="221" priority="371">
+    <cfRule type="expression" dxfId="220" priority="371">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="220" priority="372">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E83:Q83 Q124:Q125">
@@ -19921,25 +19915,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111">
-    <cfRule type="expression" dxfId="216" priority="43">
-      <formula>$B111=3</formula>
+    <cfRule type="expression" dxfId="216" priority="45">
+      <formula>$B111&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="215" priority="44">
       <formula>$B111=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="214" priority="45">
-      <formula>$B111&lt;2</formula>
+    <cfRule type="expression" dxfId="214" priority="43">
+      <formula>$B111=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109:G110">
-    <cfRule type="expression" dxfId="213" priority="46">
-      <formula>$B109=3</formula>
+    <cfRule type="expression" dxfId="213" priority="48">
+      <formula>$B109&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="212" priority="47">
       <formula>$B109=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="211" priority="48">
-      <formula>$B109&lt;2</formula>
+    <cfRule type="expression" dxfId="211" priority="46">
+      <formula>$B109=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51:I54">
@@ -19968,36 +19962,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:I99 F100 H100:I100 F101:I101 F102 H102:I102">
-    <cfRule type="expression" dxfId="203" priority="162">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="203" priority="164">
+      <formula>$B97&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="202" priority="163">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="201" priority="164">
-      <formula>$B97&lt;2</formula>
+    <cfRule type="expression" dxfId="201" priority="162">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:I101">
     <cfRule type="expression" dxfId="200" priority="32">
       <formula>$B99=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="199" priority="33">
+    <cfRule type="expression" dxfId="199" priority="34">
+      <formula>$B99&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="198" priority="33">
       <formula>$B99=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="198" priority="34">
-      <formula>$B99&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:I103">
-    <cfRule type="expression" dxfId="197" priority="7">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="197" priority="9">
+      <formula>$B102&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="196" priority="8">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="195" priority="9">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="195" priority="7">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:I103">
@@ -20022,36 +20016,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G100">
-    <cfRule type="expression" dxfId="189" priority="29">
-      <formula>$B100=3</formula>
+    <cfRule type="expression" dxfId="189" priority="31">
+      <formula>$B100&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="188" priority="30">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="187" priority="31">
-      <formula>$B100&lt;2</formula>
+    <cfRule type="expression" dxfId="187" priority="29">
+      <formula>$B100=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G102">
-    <cfRule type="expression" dxfId="186" priority="4">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="186" priority="6">
+      <formula>$B102&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="185" priority="5">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="6">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="184" priority="4">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G106:I107">
-    <cfRule type="expression" dxfId="183" priority="756">
-      <formula>$B106=3</formula>
+    <cfRule type="expression" dxfId="183" priority="758">
+      <formula>$B106&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="182" priority="757">
       <formula>$B106=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="758">
-      <formula>$B106&lt;2</formula>
+    <cfRule type="expression" dxfId="181" priority="756">
+      <formula>$B106=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="180" priority="759">
       <formula>$B106=0</formula>
@@ -20069,36 +20063,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H145:H146">
-    <cfRule type="expression" dxfId="176" priority="1031">
-      <formula>$B146=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="175" priority="1032">
+    <cfRule type="expression" dxfId="176" priority="1032">
       <formula>$B146&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="1034">
+    <cfRule type="expression" dxfId="175" priority="1034">
       <formula>$B146=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="174" priority="1031">
+      <formula>$B146=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5">
-    <cfRule type="expression" dxfId="173" priority="562">
-      <formula>$B5=3</formula>
+    <cfRule type="expression" dxfId="173" priority="563">
+      <formula>$B5=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="563">
-      <formula>$B5=2</formula>
+    <cfRule type="expression" dxfId="172" priority="565">
+      <formula>$B5=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="171" priority="564">
       <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="565">
-      <formula>$B5=0</formula>
+    <cfRule type="expression" dxfId="170" priority="562">
+      <formula>$B5=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J71:L73">
-    <cfRule type="expression" dxfId="169" priority="613">
+    <cfRule type="expression" dxfId="169" priority="617">
+      <formula>$B71=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="168" priority="613">
       <formula>_xlfn.ISFORMULA(J71)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="168" priority="617">
-      <formula>$B71=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:Q96 J104:Q1048576">
@@ -20112,14 +20106,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69:S73">
-    <cfRule type="expression" dxfId="165" priority="609">
-      <formula>$B69=3</formula>
+    <cfRule type="expression" dxfId="165" priority="611">
+      <formula>$B69&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="164" priority="610">
       <formula>$B69=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="163" priority="611">
-      <formula>$B69&lt;2</formula>
+    <cfRule type="expression" dxfId="163" priority="609">
+      <formula>$B69=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 J69:S70 U69:V73">
@@ -20128,14 +20122,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 U69:V73">
-    <cfRule type="expression" dxfId="161" priority="619">
-      <formula>$B68=3</formula>
+    <cfRule type="expression" dxfId="161" priority="621">
+      <formula>$B68&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="160" priority="620">
       <formula>$B68=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="159" priority="621">
-      <formula>$B68&lt;2</formula>
+    <cfRule type="expression" dxfId="159" priority="619">
+      <formula>$B68=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
@@ -20171,14 +20165,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M101">
-    <cfRule type="expression" dxfId="150" priority="132">
+    <cfRule type="expression" dxfId="150" priority="134">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="132">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="133">
+    <cfRule type="expression" dxfId="148" priority="133">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="134">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M103">
@@ -20201,33 +20195,33 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K102:M102">
-    <cfRule type="expression" dxfId="142" priority="23">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="142" priority="25">
+      <formula>$B102&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="141" priority="24">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="25">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="140" priority="23">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K142:M143">
     <cfRule type="expression" dxfId="139" priority="720">
       <formula>$B142=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="721">
-      <formula>$B142=2</formula>
+    <cfRule type="expression" dxfId="138" priority="723">
+      <formula>$B142=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="137" priority="722">
       <formula>$B142&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="723">
-      <formula>$B142=0</formula>
+    <cfRule type="expression" dxfId="136" priority="721">
+      <formula>$B142=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112">
-    <cfRule type="expression" dxfId="135" priority="569">
-      <formula>$B112=0</formula>
+    <cfRule type="expression" dxfId="135" priority="962">
+      <formula>#REF!=3</formula>
     </cfRule>
     <cfRule type="expression" dxfId="134" priority="959">
       <formula>#REF!=2</formula>
@@ -20235,11 +20229,11 @@
     <cfRule type="expression" dxfId="133" priority="960">
       <formula>#REF!&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="961">
+    <cfRule type="expression" dxfId="132" priority="569">
+      <formula>$B112=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="961">
       <formula>#REF!=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="131" priority="962">
-      <formula>#REF!=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112:V112">
@@ -20254,14 +20248,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M103">
-    <cfRule type="expression" dxfId="127" priority="170">
-      <formula>$B103=3</formula>
+    <cfRule type="expression" dxfId="127" priority="172">
+      <formula>$B103&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="126" priority="171">
       <formula>$B103=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="172">
-      <formula>$B103&lt;2</formula>
+    <cfRule type="expression" dxfId="125" priority="170">
+      <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N81">
@@ -20270,14 +20264,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O97:O98">
-    <cfRule type="expression" dxfId="123" priority="290">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="123" priority="292">
+      <formula>$B97&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="122" priority="291">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="292">
-      <formula>$B97&lt;2</formula>
+    <cfRule type="expression" dxfId="121" priority="290">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O97:O103">
@@ -20298,14 +20292,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O99:O103">
-    <cfRule type="expression" dxfId="115" priority="278">
-      <formula>$B99=3</formula>
+    <cfRule type="expression" dxfId="115" priority="280">
+      <formula>$B99&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="114" priority="279">
       <formula>$B99=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="280">
-      <formula>$B99&lt;2</formula>
+    <cfRule type="expression" dxfId="113" priority="278">
+      <formula>$B99=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71:Q73">
@@ -20319,11 +20313,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q149">
-    <cfRule type="expression" dxfId="110" priority="777">
+    <cfRule type="expression" dxfId="110" priority="778">
+      <formula>$B150=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="109" priority="777">
       <formula>$B150=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="778">
-      <formula>$B150=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="108" priority="779">
       <formula>$B150&lt;2</formula>
@@ -20333,58 +20327,58 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:R98">
-    <cfRule type="expression" dxfId="106" priority="258">
+    <cfRule type="expression" dxfId="106" priority="259">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="258">
       <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="105" priority="259">
-      <formula>$B97=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="104" priority="260">
       <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:R100">
-    <cfRule type="expression" dxfId="103" priority="251">
+    <cfRule type="expression" dxfId="103" priority="253">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="251">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="252">
+    <cfRule type="expression" dxfId="101" priority="252">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="253">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:R101">
-    <cfRule type="expression" dxfId="100" priority="100">
-      <formula>$B101=3</formula>
+    <cfRule type="expression" dxfId="100" priority="102">
+      <formula>$B101&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="99" priority="101">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="102">
-      <formula>$B101&lt;2</formula>
+    <cfRule type="expression" dxfId="98" priority="100">
+      <formula>$B101=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q102:R102">
-    <cfRule type="expression" dxfId="97" priority="20">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="97" priority="22">
+      <formula>$B102&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="96" priority="21">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="22">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="95" priority="20">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q103:R103">
-    <cfRule type="expression" dxfId="94" priority="93">
-      <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="94">
+    <cfRule type="expression" dxfId="94" priority="94">
       <formula>$B103=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="95">
+    <cfRule type="expression" dxfId="93" priority="95">
       <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="93">
+      <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71:S73">
@@ -20426,14 +20420,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q103:S103">
-    <cfRule type="expression" dxfId="81" priority="86">
-      <formula>$B103=3</formula>
+    <cfRule type="expression" dxfId="81" priority="88">
+      <formula>$B103&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="80" priority="87">
       <formula>$B103=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="88">
-      <formula>$B103&lt;2</formula>
+    <cfRule type="expression" dxfId="79" priority="86">
+      <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:T103">
@@ -20442,53 +20436,53 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:S100">
-    <cfRule type="expression" dxfId="77" priority="237">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="238">
+    <cfRule type="expression" dxfId="77" priority="238">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="239">
+    <cfRule type="expression" dxfId="76" priority="239">
       <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="237">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S102">
     <cfRule type="expression" dxfId="74" priority="14">
       <formula>$B102=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="15">
+    <cfRule type="expression" dxfId="73" priority="16">
+      <formula>$B102&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="15">
       <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="16">
-      <formula>$B102&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S152">
-    <cfRule type="expression" dxfId="71" priority="704">
-      <formula>$B152=3</formula>
+    <cfRule type="expression" dxfId="71" priority="707">
+      <formula>$B152=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="70" priority="705">
       <formula>$B152=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="706">
+    <cfRule type="expression" dxfId="69" priority="704">
+      <formula>$B152=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="706">
       <formula>$B152&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="707">
-      <formula>$B152=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S156:S157">
     <cfRule type="expression" dxfId="67" priority="700">
       <formula>$B156=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="701">
-      <formula>$B156=2</formula>
+    <cfRule type="expression" dxfId="66" priority="703">
+      <formula>$B156=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="65" priority="702">
       <formula>$B156&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="703">
-      <formula>$B156=0</formula>
+    <cfRule type="expression" dxfId="64" priority="701">
+      <formula>$B156=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:T98">
@@ -20517,11 +20511,11 @@
     <cfRule type="expression" dxfId="57" priority="65">
       <formula>$B103=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="66">
+    <cfRule type="expression" dxfId="56" priority="67">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="66">
       <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="67">
-      <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S90:V93">
@@ -20530,45 +20524,45 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S150:V151">
-    <cfRule type="expression" dxfId="53" priority="664">
-      <formula>$B150=3</formula>
+    <cfRule type="expression" dxfId="53" priority="667">
+      <formula>$B150=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="665">
       <formula>$B150=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="666">
+    <cfRule type="expression" dxfId="51" priority="664">
+      <formula>$B150=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="666">
       <formula>$B150&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="667">
-      <formula>$B150=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5">
-    <cfRule type="expression" dxfId="49" priority="457">
-      <formula>$B5=0</formula>
+    <cfRule type="expression" dxfId="49" priority="460">
+      <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="458">
+    <cfRule type="expression" dxfId="48" priority="459">
+      <formula>$B5=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="458">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="459">
-      <formula>$B5=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="460">
-      <formula>$B5&lt;2</formula>
+    <cfRule type="expression" dxfId="46" priority="457">
+      <formula>$B5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6">
-    <cfRule type="expression" dxfId="45" priority="1015">
+    <cfRule type="expression" dxfId="45" priority="1020">
+      <formula>$B5=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="1015">
       <formula>$B5=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="1016">
+    <cfRule type="expression" dxfId="43" priority="1016">
       <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="1018">
+    <cfRule type="expression" dxfId="42" priority="1018">
       <formula>$B5=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="1020">
-      <formula>$B5=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T97:T100">
@@ -20597,11 +20591,11 @@
     <cfRule type="expression" dxfId="35" priority="1">
       <formula>$B100=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="2">
+    <cfRule type="expression" dxfId="34" priority="3">
+      <formula>$B100&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="2">
       <formula>$B100=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="3">
-      <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T102:T103">
@@ -20616,17 +20610,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U106">
-    <cfRule type="expression" dxfId="29" priority="785">
-      <formula>$B105=3</formula>
+    <cfRule type="expression" dxfId="29" priority="788">
+      <formula>$B105=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="786">
+    <cfRule type="expression" dxfId="28" priority="787">
+      <formula>$B105&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="786">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="787">
-      <formula>$B105&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="788">
-      <formula>$B105=0</formula>
+    <cfRule type="expression" dxfId="26" priority="785">
+      <formula>$B105=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U135:AG140">
@@ -20635,39 +20629,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W97:W103">
-    <cfRule type="expression" dxfId="24" priority="212">
+    <cfRule type="expression" dxfId="24" priority="214">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="212">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="213">
+    <cfRule type="expression" dxfId="22" priority="213">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="214">
-      <formula>$B97&lt;2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="21" priority="215">
       <formula>$B97=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W76:AG82">
-    <cfRule type="expression" dxfId="20" priority="505">
-      <formula>$B76=3</formula>
+    <cfRule type="expression" dxfId="20" priority="508">
+      <formula>$B76=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="506">
+    <cfRule type="expression" dxfId="19" priority="507">
+      <formula>$B76&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="506">
       <formula>$B76=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="507">
-      <formula>$B76&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="508">
-      <formula>$B76=0</formula>
+    <cfRule type="expression" dxfId="17" priority="505">
+      <formula>$B76=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W95:AG96 A145:G146 I145:R146 A147:R147">
-    <cfRule type="expression" dxfId="16" priority="709">
+    <cfRule type="expression" dxfId="16" priority="710">
+      <formula>$B95&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="709">
       <formula>$B95=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="710">
-      <formula>$B95&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W106:AG108">
@@ -20701,17 +20695,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z97:AG103">
-    <cfRule type="expression" dxfId="6" priority="54">
-      <formula>$B97=3</formula>
+    <cfRule type="expression" dxfId="6" priority="57">
+      <formula>$B97=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="55">
+    <cfRule type="expression" dxfId="5" priority="56">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="55">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="56">
-      <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="57">
-      <formula>$B97=0</formula>
+    <cfRule type="expression" dxfId="3" priority="54">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z133:AG133">
@@ -20807,20 +20801,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="154" t="s">
         <v>418</v>
       </c>
-      <c r="B1" s="158" t="s">
+      <c r="B1" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="157" t="s">
+      <c r="C1" s="151" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="143"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
@@ -21724,12 +21718,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="155" t="s">
         <v>473</v>
       </c>
-      <c r="B2" s="161"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="162"/>
+      <c r="B2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="157"/>
     </row>
     <row r="3" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
@@ -21786,12 +21780,12 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="160" t="s">
+      <c r="A7" s="155" t="s">
         <v>361</v>
       </c>
-      <c r="B7" s="161"/>
-      <c r="C7" s="161"/>
-      <c r="D7" s="162"/>
+      <c r="B7" s="156"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="157"/>
     </row>
     <row r="8" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
@@ -21850,12 +21844,12 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="160" t="s">
+      <c r="A12" s="155" t="s">
         <v>236</v>
       </c>
-      <c r="B12" s="161"/>
-      <c r="C12" s="161"/>
-      <c r="D12" s="162"/>
+      <c r="B12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="157"/>
     </row>
     <row r="13" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
@@ -21954,12 +21948,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="160" t="s">
+      <c r="A20" s="155" t="s">
         <v>503</v>
       </c>
-      <c r="B20" s="161"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="162"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="157"/>
     </row>
     <row r="21" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
@@ -22088,12 +22082,12 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="160" t="s">
+      <c r="A30" s="155" t="s">
         <v>516</v>
       </c>
-      <c r="B30" s="161"/>
-      <c r="C30" s="161"/>
-      <c r="D30" s="162"/>
+      <c r="B30" s="156"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="157"/>
     </row>
     <row r="31" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="20" t="s">
@@ -22168,12 +22162,12 @@
       <c r="D36" s="26"/>
     </row>
     <row r="37" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="160" t="s">
+      <c r="A37" s="155" t="s">
         <v>524</v>
       </c>
-      <c r="B37" s="161"/>
-      <c r="C37" s="161"/>
-      <c r="D37" s="162"/>
+      <c r="B37" s="156"/>
+      <c r="C37" s="156"/>
+      <c r="D37" s="157"/>
     </row>
     <row r="38" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
@@ -22260,12 +22254,12 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="160" t="s">
+      <c r="A44" s="155" t="s">
         <v>537</v>
       </c>
-      <c r="B44" s="161"/>
-      <c r="C44" s="161"/>
-      <c r="D44" s="162"/>
+      <c r="B44" s="156"/>
+      <c r="C44" s="156"/>
+      <c r="D44" s="157"/>
     </row>
     <row r="45" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
@@ -22282,12 +22276,12 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="160" t="s">
+      <c r="A46" s="155" t="s">
         <v>540</v>
       </c>
-      <c r="B46" s="161"/>
-      <c r="C46" s="161"/>
-      <c r="D46" s="162"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="156"/>
+      <c r="D46" s="157"/>
     </row>
     <row r="47" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
@@ -22332,12 +22326,12 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="160" t="s">
+      <c r="A50" s="155" t="s">
         <v>547</v>
       </c>
-      <c r="B50" s="161"/>
-      <c r="C50" s="161"/>
-      <c r="D50" s="162"/>
+      <c r="B50" s="156"/>
+      <c r="C50" s="156"/>
+      <c r="D50" s="157"/>
     </row>
     <row r="51" spans="1:4" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
@@ -22438,7 +22432,7 @@
         <v>4.4866666666666672</v>
       </c>
       <c r="G2" s="2">
-        <f>AVERAGE(C2,E2)</f>
+        <f t="shared" ref="G2:G43" si="0">AVERAGE(C2,E2)</f>
         <v>4.8245000000000005</v>
       </c>
       <c r="J2" s="85"/>
@@ -22467,7 +22461,7 @@
         <v>3.5062697462593384</v>
       </c>
       <c r="G3" s="2">
-        <f>AVERAGE(C3,E3)</f>
+        <f t="shared" si="0"/>
         <v>3.686341568331442</v>
       </c>
       <c r="J3" s="85"/>
@@ -22492,11 +22486,11 @@
         <v>3.957082035561005</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F42" si="0">(C4+D4+E4)/3</f>
+        <f t="shared" ref="F4:F43" si="1">(C4+D4+E4)/3</f>
         <v>3.4393954496349726</v>
       </c>
       <c r="G4" s="2">
-        <f>AVERAGE(C4,E4)</f>
+        <f t="shared" si="0"/>
         <v>3.5828549320799725</v>
       </c>
       <c r="J4" s="85"/>
@@ -22521,11 +22515,11 @@
         <v>3.9210211421628185</v>
       </c>
       <c r="F5" s="2">
+        <f t="shared" si="1"/>
+        <v>3.3738149319503319</v>
+      </c>
+      <c r="G5" s="2">
         <f t="shared" si="0"/>
-        <v>3.3738149319503319</v>
-      </c>
-      <c r="G5" s="2">
-        <f>AVERAGE(C5,E5)</f>
         <v>3.5161408231822495</v>
       </c>
       <c r="J5" s="85"/>
@@ -22550,11 +22544,11 @@
         <v>3.7360351953690305</v>
       </c>
       <c r="F6" s="2">
+        <f t="shared" si="1"/>
+        <v>3.2172169877397194</v>
+      </c>
+      <c r="G6" s="2">
         <f t="shared" si="0"/>
-        <v>3.2172169877397194</v>
-      </c>
-      <c r="G6" s="2">
-        <f>AVERAGE(C6,E6)</f>
         <v>3.3629301145082025</v>
       </c>
       <c r="J6" s="85"/>
@@ -22579,11 +22573,11 @@
         <v>3.5114258977149078</v>
       </c>
       <c r="F7" s="2">
+        <f t="shared" si="1"/>
+        <v>3.0787504404812402</v>
+      </c>
+      <c r="G7" s="2">
         <f t="shared" si="0"/>
-        <v>3.0787504404812402</v>
-      </c>
-      <c r="G7" s="2">
-        <f>AVERAGE(C7,E7)</f>
         <v>3.2019629488574539</v>
       </c>
       <c r="J7" s="85"/>
@@ -22608,11 +22602,11 @@
         <v>3.4175275615567915</v>
       </c>
       <c r="F8" s="2">
+        <f t="shared" si="1"/>
+        <v>3.0039255201733899</v>
+      </c>
+      <c r="G8" s="2">
         <f t="shared" si="0"/>
-        <v>3.0039255201733899</v>
-      </c>
-      <c r="G8" s="2">
-        <f>AVERAGE(C8,E8)</f>
         <v>3.0914027849277734</v>
       </c>
       <c r="J8" s="85"/>
@@ -22637,11 +22631,11 @@
         <v>3.3052945650086425</v>
       </c>
       <c r="F9" s="2">
+        <f t="shared" si="1"/>
+        <v>2.9241383099779572</v>
+      </c>
+      <c r="G9" s="2">
         <f t="shared" si="0"/>
-        <v>2.9241383099779572</v>
-      </c>
-      <c r="G9" s="2">
-        <f>AVERAGE(C9,E9)</f>
         <v>2.9807301840587259</v>
       </c>
       <c r="J9" s="85"/>
@@ -22666,11 +22660,11 @@
         <v>3.169357706709226</v>
       </c>
       <c r="F10" s="2">
+        <f t="shared" si="1"/>
+        <v>2.8352148370361179</v>
+      </c>
+      <c r="G10" s="2">
         <f t="shared" si="0"/>
-        <v>2.8352148370361179</v>
-      </c>
-      <c r="G10" s="2">
-        <f>AVERAGE(C10,E10)</f>
         <v>2.8717240445481238</v>
       </c>
       <c r="J10" s="85"/>
@@ -22695,11 +22689,11 @@
         <v>2.9935068645640079</v>
       </c>
       <c r="F11" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7057089290236824</v>
+      </c>
+      <c r="G11" s="2">
         <f t="shared" si="0"/>
-        <v>2.7057089290236824</v>
-      </c>
-      <c r="G11" s="2">
-        <f>AVERAGE(C11,E11)</f>
         <v>2.7428865661638291</v>
       </c>
       <c r="J11" s="85"/>
@@ -22724,11 +22718,11 @@
         <v>2.9062257345491385</v>
       </c>
       <c r="F12" s="2">
+        <f t="shared" si="1"/>
+        <v>2.6125528777402565</v>
+      </c>
+      <c r="G12" s="2">
         <f t="shared" si="0"/>
-        <v>2.6125528777402565</v>
-      </c>
-      <c r="G12" s="2">
-        <f>AVERAGE(C12,E12)</f>
         <v>2.6547572956914456</v>
       </c>
       <c r="J12" s="85"/>
@@ -22753,11 +22747,11 @@
         <v>2.8565425394190873</v>
       </c>
       <c r="F13" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5517844529550797</v>
+      </c>
+      <c r="G13" s="2">
         <f t="shared" si="0"/>
-        <v>2.5517844529550797</v>
-      </c>
-      <c r="G13" s="2">
-        <f>AVERAGE(C13,E13)</f>
         <v>2.6090508586535548</v>
       </c>
       <c r="J13" s="85"/>
@@ -22782,11 +22776,11 @@
         <v>2.7957551656920079</v>
       </c>
       <c r="F14" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5075967787513953</v>
+      </c>
+      <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>2.5075967787513953</v>
-      </c>
-      <c r="G14" s="2">
-        <f>AVERAGE(C14,E14)</f>
         <v>2.5496784815670548</v>
       </c>
       <c r="J14" s="85"/>
@@ -22811,11 +22805,11 @@
         <v>2.7305519276534986</v>
       </c>
       <c r="F15" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4523237722327944</v>
+      </c>
+      <c r="G15" s="2">
         <f t="shared" si="0"/>
-        <v>2.4523237722327944</v>
-      </c>
-      <c r="G15" s="2">
-        <f>AVERAGE(C15,E15)</f>
         <v>2.4875932423717142</v>
       </c>
       <c r="J15" s="85"/>
@@ -22840,11 +22834,11 @@
         <v>2.6719109087145525</v>
       </c>
       <c r="F16" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4141728726939413</v>
+      </c>
+      <c r="G16" s="2">
         <f t="shared" si="0"/>
-        <v>2.4141728726939413</v>
-      </c>
-      <c r="G16" s="2">
-        <f>AVERAGE(C16,E16)</f>
         <v>2.424540883955447</v>
       </c>
       <c r="J16" s="85"/>
@@ -22869,11 +22863,11 @@
         <v>2.6550113847894279</v>
       </c>
       <c r="F17" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3767869054283635</v>
+      </c>
+      <c r="G17" s="2">
         <f t="shared" si="0"/>
-        <v>2.3767869054283635</v>
-      </c>
-      <c r="G17" s="2">
-        <f>AVERAGE(C17,E17)</f>
         <v>2.3799883203163819</v>
       </c>
       <c r="J17" s="85"/>
@@ -22898,11 +22892,11 @@
         <v>2.626914596794709</v>
       </c>
       <c r="F18" s="2">
+        <f t="shared" si="1"/>
+        <v>2.3272917676610168</v>
+      </c>
+      <c r="G18" s="2">
         <f t="shared" si="0"/>
-        <v>2.3272917676610168</v>
-      </c>
-      <c r="G18" s="2">
-        <f>AVERAGE(C18,E18)</f>
         <v>2.317119948999764</v>
       </c>
       <c r="J18" s="85"/>
@@ -22927,11 +22921,11 @@
         <v>2.5433233042707251</v>
       </c>
       <c r="F19" s="2">
+        <f t="shared" si="1"/>
+        <v>2.2767513153595522</v>
+      </c>
+      <c r="G19" s="2">
         <f t="shared" si="0"/>
-        <v>2.2767513153595522</v>
-      </c>
-      <c r="G19" s="2">
-        <f>AVERAGE(C19,E19)</f>
         <v>2.2302807545519334</v>
       </c>
       <c r="J19" s="85"/>
@@ -22956,11 +22950,11 @@
         <v>2.5197406861548979</v>
       </c>
       <c r="F20" s="2">
+        <f t="shared" si="1"/>
+        <v>2.2412800619923652</v>
+      </c>
+      <c r="G20" s="2">
         <f t="shared" si="0"/>
-        <v>2.2412800619923652</v>
-      </c>
-      <c r="G20" s="2">
-        <f>AVERAGE(C20,E20)</f>
         <v>2.1870155851475661</v>
       </c>
       <c r="J20" s="85"/>
@@ -22985,11 +22979,11 @@
         <v>2.4774246149417012</v>
       </c>
       <c r="F21" s="2">
+        <f t="shared" si="1"/>
+        <v>2.189412517515426</v>
+      </c>
+      <c r="G21" s="2">
         <f t="shared" si="0"/>
-        <v>2.189412517515426</v>
-      </c>
-      <c r="G21" s="2">
-        <f>AVERAGE(C21,E21)</f>
         <v>2.1339729200447355</v>
       </c>
       <c r="J21" s="85"/>
@@ -23014,11 +23008,11 @@
         <v>2.3858419851208348</v>
       </c>
       <c r="F22" s="2">
+        <f t="shared" si="1"/>
+        <v>2.0735321854825766</v>
+      </c>
+      <c r="G22" s="2">
         <f t="shared" si="0"/>
-        <v>2.0735321854825766</v>
-      </c>
-      <c r="G22" s="2">
-        <f>AVERAGE(C22,E22)</f>
         <v>2.0624825791992483</v>
       </c>
       <c r="J22" s="85"/>
@@ -23043,11 +23037,11 @@
         <v>2.2928196811581327</v>
       </c>
       <c r="F23" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9906268265147744</v>
+      </c>
+      <c r="G23" s="2">
         <f t="shared" si="0"/>
-        <v>1.9906268265147744</v>
-      </c>
-      <c r="G23" s="2">
-        <f>AVERAGE(C23,E23)</f>
         <v>1.9880769282274622</v>
       </c>
       <c r="J23" s="85"/>
@@ -23072,11 +23066,11 @@
         <v>2.1163260400868955</v>
       </c>
       <c r="F24" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8741277033823094</v>
+      </c>
+      <c r="G24" s="2">
         <f t="shared" si="0"/>
-        <v>1.8741277033823094</v>
-      </c>
-      <c r="G24" s="2">
-        <f>AVERAGE(C24,E24)</f>
         <v>1.8724738704833306</v>
       </c>
       <c r="J24" s="85"/>
@@ -23101,11 +23095,11 @@
         <v>1.9426595831138538</v>
       </c>
       <c r="F25" s="2">
+        <f t="shared" si="1"/>
+        <v>1.7857892482145872</v>
+      </c>
+      <c r="G25" s="2">
         <f t="shared" si="0"/>
-        <v>1.7857892482145872</v>
-      </c>
-      <c r="G25" s="2">
-        <f>AVERAGE(C25,E25)</f>
         <v>1.7549986532690625</v>
       </c>
       <c r="J25" s="85"/>
@@ -23130,11 +23124,11 @@
         <v>1.8946134742404235</v>
       </c>
       <c r="F26" s="2">
+        <f t="shared" si="1"/>
+        <v>1.7101548189503319</v>
+      </c>
+      <c r="G26" s="2">
         <f t="shared" si="0"/>
-        <v>1.7101548189503319</v>
-      </c>
-      <c r="G26" s="2">
-        <f>AVERAGE(C26,E26)</f>
         <v>1.7039279905262064</v>
       </c>
       <c r="J26" s="85"/>
@@ -23159,11 +23153,11 @@
         <v>1.8701827875977977</v>
       </c>
       <c r="F27" s="2">
+        <f t="shared" si="1"/>
+        <v>1.7186293403655928</v>
+      </c>
+      <c r="G27" s="2">
         <f t="shared" si="0"/>
-        <v>1.7186293403655928</v>
-      </c>
-      <c r="G27" s="2">
-        <f>AVERAGE(C27,E27)</f>
         <v>1.6835550056587372</v>
       </c>
       <c r="J27" s="85"/>
@@ -23188,11 +23182,11 @@
         <v>1.8817700415482179</v>
       </c>
       <c r="F28" s="2">
+        <f t="shared" si="1"/>
+        <v>1.7008450267028763</v>
+      </c>
+      <c r="G28" s="2">
         <f t="shared" si="0"/>
-        <v>1.7008450267028763</v>
-      </c>
-      <c r="G28" s="2">
-        <f>AVERAGE(C28,E28)</f>
         <v>1.6813650207741091</v>
       </c>
       <c r="J28" s="85"/>
@@ -23217,11 +23211,11 @@
         <v>1.804179411559159</v>
       </c>
       <c r="F29" s="2">
+        <f t="shared" si="1"/>
+        <v>1.6506685282829718</v>
+      </c>
+      <c r="G29" s="2">
         <f t="shared" si="0"/>
-        <v>1.6506685282829718</v>
-      </c>
-      <c r="G29" s="2">
-        <f>AVERAGE(C29,E29)</f>
         <v>1.6347546134312945</v>
       </c>
       <c r="J29" s="85"/>
@@ -23246,11 +23240,11 @@
         <v>1.6867141354415081</v>
       </c>
       <c r="F30" s="2">
+        <f t="shared" si="1"/>
+        <v>1.591094769668852</v>
+      </c>
+      <c r="G30" s="2">
         <f t="shared" si="0"/>
-        <v>1.591094769668852</v>
-      </c>
-      <c r="G30" s="2">
-        <f>AVERAGE(C30,E30)</f>
         <v>1.5646038209675073</v>
       </c>
       <c r="J30" s="85"/>
@@ -23275,11 +23269,11 @@
         <v>1.6270248440158814</v>
       </c>
       <c r="F31" s="2">
+        <f t="shared" si="1"/>
+        <v>1.5523759599503857</v>
+      </c>
+      <c r="G31" s="2">
         <f t="shared" si="0"/>
-        <v>1.5523759599503857</v>
-      </c>
-      <c r="G31" s="2">
-        <f>AVERAGE(C31,E31)</f>
         <v>1.5200773075041236</v>
       </c>
       <c r="J31" s="85"/>
@@ -23304,11 +23298,11 @@
         <v>1.5664099993932403</v>
       </c>
       <c r="F32" s="2">
+        <f t="shared" si="1"/>
+        <v>1.5124689178253268</v>
+      </c>
+      <c r="G32" s="2">
         <f t="shared" si="0"/>
-        <v>1.5124689178253268</v>
-      </c>
-      <c r="G32" s="2">
-        <f>AVERAGE(C32,E32)</f>
         <v>1.479726738827055</v>
       </c>
       <c r="J32" s="85"/>
@@ -23333,11 +23327,11 @@
         <v>1.5228434272231235</v>
       </c>
       <c r="F33" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4906765539959703</v>
+      </c>
+      <c r="G33" s="2">
         <f t="shared" si="0"/>
-        <v>1.4906765539959703</v>
-      </c>
-      <c r="G33" s="2">
-        <f>AVERAGE(C33,E33)</f>
         <v>1.4436821558720041</v>
       </c>
       <c r="J33" s="85"/>
@@ -23362,11 +23356,11 @@
         <v>1.5002326359832638</v>
       </c>
       <c r="F34" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4727918335049139</v>
+      </c>
+      <c r="G34" s="2">
         <f t="shared" si="0"/>
-        <v>1.4727918335049139</v>
-      </c>
-      <c r="G34" s="2">
-        <f>AVERAGE(C34,E34)</f>
         <v>1.4181516026748717</v>
       </c>
       <c r="J34" s="85"/>
@@ -23391,11 +23385,11 @@
         <v>1.4653613282247768</v>
       </c>
       <c r="F35" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4319254340913525</v>
+      </c>
+      <c r="G35" s="2">
         <f t="shared" si="0"/>
-        <v>1.4319254340913525</v>
-      </c>
-      <c r="G35" s="2">
-        <f>AVERAGE(C35,E35)</f>
         <v>1.3845116500278811</v>
       </c>
       <c r="J35" s="85"/>
@@ -23420,11 +23414,11 @@
         <v>1.4135685922356678</v>
       </c>
       <c r="F36" s="2">
+        <f t="shared" si="1"/>
+        <v>1.372621588114268</v>
+      </c>
+      <c r="G36" s="2">
         <f t="shared" si="0"/>
-        <v>1.372621588114268</v>
-      </c>
-      <c r="G36" s="2">
-        <f>AVERAGE(C36,E36)</f>
         <v>1.3412397416623882</v>
       </c>
       <c r="J36" s="85"/>
@@ -23449,11 +23443,11 @@
         <v>1.3779926445861912</v>
       </c>
       <c r="F37" s="2">
+        <f t="shared" si="1"/>
+        <v>1.3480058670420119</v>
+      </c>
+      <c r="G37" s="2">
         <f t="shared" si="0"/>
-        <v>1.3480058670420119</v>
-      </c>
-      <c r="G37" s="2">
-        <f>AVERAGE(C37,E37)</f>
         <v>1.3042400445973794</v>
       </c>
       <c r="J37" s="85"/>
@@ -23478,11 +23472,11 @@
         <v>1.3590946670176363</v>
       </c>
       <c r="F38" s="2">
+        <f t="shared" si="1"/>
+        <v>1.3235908015739473</v>
+      </c>
+      <c r="G38" s="2">
         <f t="shared" si="0"/>
-        <v>1.3235908015739473</v>
-      </c>
-      <c r="G38" s="2">
-        <f>AVERAGE(C38,E38)</f>
         <v>1.2779956093708869</v>
       </c>
       <c r="J38" s="85"/>
@@ -23507,11 +23501,11 @@
         <v>1.2994960627780956</v>
       </c>
       <c r="F39" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1922077853396449</v>
+      </c>
+      <c r="G39" s="2">
         <f t="shared" si="0"/>
-        <v>1.1922077853396449</v>
-      </c>
-      <c r="G39" s="2">
-        <f>AVERAGE(C39,E39)</f>
         <v>1.2306685334810981</v>
       </c>
       <c r="J39" s="85"/>
@@ -23536,11 +23530,11 @@
         <v>1.1498296122510112</v>
       </c>
       <c r="F40" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0857693185859105</v>
+      </c>
+      <c r="G40" s="2">
         <f t="shared" si="0"/>
-        <v>1.0857693185859105</v>
-      </c>
-      <c r="G40" s="2">
-        <f>AVERAGE(C40,E40)</f>
         <v>1.1332526077340848</v>
       </c>
       <c r="J40" s="85"/>
@@ -23565,11 +23559,11 @@
         <v>1.0652117467060798</v>
       </c>
       <c r="F41" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0519580204466237</v>
+      </c>
+      <c r="G41" s="2">
         <f t="shared" si="0"/>
-        <v>1.0519580204466237</v>
-      </c>
-      <c r="G41" s="2">
-        <f>AVERAGE(C41,E41)</f>
         <v>1.0679786239957139</v>
       </c>
       <c r="J41" s="85"/>
@@ -23594,11 +23588,11 @@
         <v>1.06</v>
       </c>
       <c r="F42" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0433333333333334</v>
+      </c>
+      <c r="G42" s="2">
         <f t="shared" si="0"/>
-        <v>1.0433333333333334</v>
-      </c>
-      <c r="G42" s="2">
-        <f>AVERAGE(C42,E42)</f>
         <v>1.05</v>
       </c>
       <c r="J42" s="85"/>
@@ -23620,6 +23614,14 @@
         <v>1</v>
       </c>
       <c r="E43" s="85">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J43" s="85"/>
@@ -23723,13 +23725,13 @@
       <c r="B9">
         <v>0.08</v>
       </c>
-      <c r="C9" s="163" t="s">
+      <c r="C9" s="158" t="s">
         <v>561</v>
       </c>
-      <c r="D9" s="163" t="s">
+      <c r="D9" s="158" t="s">
         <v>562</v>
       </c>
-      <c r="E9" s="163" t="s">
+      <c r="E9" s="158" t="s">
         <v>563</v>
       </c>
     </row>
@@ -23740,9 +23742,9 @@
       <c r="B10">
         <v>0</v>
       </c>
-      <c r="C10" s="164"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -23751,9 +23753,9 @@
       <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
+      <c r="C11" s="159"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="159"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -23762,9 +23764,9 @@
       <c r="B12">
         <v>0.18443169820109739</v>
       </c>
-      <c r="C12" s="164"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="159"/>
+      <c r="E12" s="159"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -23773,9 +23775,9 @@
       <c r="B13">
         <v>0.24138000000000001</v>
       </c>
-      <c r="C13" s="164"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="159"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -23784,9 +23786,9 @@
       <c r="B14" s="85">
         <v>0.22962848022115531</v>
       </c>
-      <c r="C14" s="164"/>
-      <c r="D14" s="164"/>
-      <c r="E14" s="164"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="159"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -23795,9 +23797,9 @@
       <c r="B15">
         <v>0.41505377678599259</v>
       </c>
-      <c r="C15" s="164"/>
-      <c r="D15" s="164"/>
-      <c r="E15" s="164"/>
+      <c r="C15" s="159"/>
+      <c r="D15" s="159"/>
+      <c r="E15" s="159"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
@@ -23806,9 +23808,9 @@
       <c r="B16">
         <v>0.39914905811401719</v>
       </c>
-      <c r="C16" s="164"/>
-      <c r="D16" s="164"/>
-      <c r="E16" s="164"/>
+      <c r="C16" s="159"/>
+      <c r="D16" s="159"/>
+      <c r="E16" s="159"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
@@ -23817,7 +23819,7 @@
       <c r="B17">
         <v>0.05</v>
       </c>
-      <c r="C17" s="164"/>
+      <c r="C17" s="159"/>
       <c r="D17" t="s">
         <v>564</v>
       </c>
@@ -24082,10 +24084,10 @@
       <c r="S3" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="141" t="s">
+      <c r="T3" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="145" t="s">
+      <c r="U3" s="164" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="108"/>
@@ -24185,8 +24187,8 @@
       <c r="S4" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="143"/>
-      <c r="U4" s="143"/>
+      <c r="T4" s="152"/>
+      <c r="U4" s="152"/>
       <c r="V4" s="108"/>
       <c r="W4" s="99" t="s">
         <v>43</v>
@@ -24278,10 +24280,10 @@
       <c r="S5" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="141" t="s">
+      <c r="T5" s="160" t="s">
         <v>63</v>
       </c>
-      <c r="U5" s="145" t="s">
+      <c r="U5" s="164" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="108"/>
@@ -24374,8 +24376,8 @@
       <c r="S6" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="143"/>
-      <c r="U6" s="143"/>
+      <c r="T6" s="152"/>
+      <c r="U6" s="152"/>
       <c r="V6" s="108"/>
       <c r="W6" s="99" t="s">
         <v>43</v>
@@ -24725,13 +24727,13 @@
       <c r="R11" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="141" t="s">
+      <c r="S11" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="141" t="s">
+      <c r="T11" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="144" t="s">
+      <c r="U11" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="108"/>
@@ -24828,9 +24830,9 @@
       <c r="R12" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="S12" s="142"/>
-      <c r="T12" s="142"/>
-      <c r="U12" s="142"/>
+      <c r="S12" s="161"/>
+      <c r="T12" s="161"/>
+      <c r="U12" s="161"/>
       <c r="V12" s="108"/>
       <c r="W12" s="99" t="s">
         <v>43</v>
@@ -24925,9 +24927,9 @@
       <c r="R13" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="S13" s="143"/>
-      <c r="T13" s="143"/>
-      <c r="U13" s="143"/>
+      <c r="S13" s="152"/>
+      <c r="T13" s="152"/>
+      <c r="U13" s="152"/>
       <c r="V13" s="108"/>
       <c r="W13" s="99" t="s">
         <v>43</v>
@@ -25278,13 +25280,13 @@
       <c r="R18" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S18" s="141" t="s">
+      <c r="S18" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T18" s="141" t="s">
+      <c r="T18" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U18" s="144" t="s">
+      <c r="U18" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V18" s="108"/>
@@ -25376,9 +25378,9 @@
       <c r="R19" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S19" s="142"/>
-      <c r="T19" s="142"/>
-      <c r="U19" s="142"/>
+      <c r="S19" s="161"/>
+      <c r="T19" s="161"/>
+      <c r="U19" s="161"/>
       <c r="V19" s="108"/>
       <c r="W19" s="99" t="s">
         <v>43</v>
@@ -25468,9 +25470,9 @@
       <c r="R20" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S20" s="143"/>
-      <c r="T20" s="143"/>
-      <c r="U20" s="143"/>
+      <c r="S20" s="152"/>
+      <c r="T20" s="152"/>
+      <c r="U20" s="152"/>
       <c r="V20" s="108"/>
       <c r="W20" s="99" t="s">
         <v>43</v>
@@ -25689,13 +25691,13 @@
       <c r="R23" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S23" s="141" t="s">
+      <c r="S23" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T23" s="141" t="s">
+      <c r="T23" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U23" s="144" t="s">
+      <c r="U23" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V23" s="108"/>
@@ -25787,9 +25789,9 @@
       <c r="R24" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S24" s="142"/>
-      <c r="T24" s="142"/>
-      <c r="U24" s="142"/>
+      <c r="S24" s="161"/>
+      <c r="T24" s="161"/>
+      <c r="U24" s="161"/>
       <c r="V24" s="108"/>
       <c r="W24" s="99" t="s">
         <v>43</v>
@@ -25879,9 +25881,9 @@
       <c r="R25" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S25" s="143"/>
-      <c r="T25" s="143"/>
-      <c r="U25" s="143"/>
+      <c r="S25" s="152"/>
+      <c r="T25" s="152"/>
+      <c r="U25" s="152"/>
       <c r="V25" s="108"/>
       <c r="W25" s="99" t="s">
         <v>43</v>
@@ -26100,13 +26102,13 @@
       <c r="R28" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S28" s="141" t="s">
+      <c r="S28" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T28" s="141" t="s">
+      <c r="T28" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U28" s="144" t="s">
+      <c r="U28" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V28" s="108"/>
@@ -26198,9 +26200,9 @@
       <c r="R29" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S29" s="142"/>
-      <c r="T29" s="142"/>
-      <c r="U29" s="142"/>
+      <c r="S29" s="161"/>
+      <c r="T29" s="161"/>
+      <c r="U29" s="161"/>
       <c r="V29" s="108"/>
       <c r="W29" s="99" t="s">
         <v>43</v>
@@ -26290,9 +26292,9 @@
       <c r="R30" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S30" s="143"/>
-      <c r="T30" s="143"/>
-      <c r="U30" s="143"/>
+      <c r="S30" s="152"/>
+      <c r="T30" s="152"/>
+      <c r="U30" s="152"/>
       <c r="V30" s="108"/>
       <c r="W30" s="99" t="s">
         <v>43</v>
@@ -26511,13 +26513,13 @@
       <c r="R33" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S33" s="141" t="s">
+      <c r="S33" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T33" s="141" t="s">
+      <c r="T33" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U33" s="144" t="s">
+      <c r="U33" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V33" s="108"/>
@@ -26609,9 +26611,9 @@
       <c r="R34" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S34" s="142"/>
-      <c r="T34" s="142"/>
-      <c r="U34" s="142"/>
+      <c r="S34" s="161"/>
+      <c r="T34" s="161"/>
+      <c r="U34" s="161"/>
       <c r="V34" s="108"/>
       <c r="W34" s="99" t="s">
         <v>43</v>
@@ -26701,9 +26703,9 @@
       <c r="R35" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S35" s="143"/>
-      <c r="T35" s="143"/>
-      <c r="U35" s="143"/>
+      <c r="S35" s="152"/>
+      <c r="T35" s="152"/>
+      <c r="U35" s="152"/>
       <c r="V35" s="108"/>
       <c r="W35" s="99" t="s">
         <v>43</v>
@@ -26922,13 +26924,13 @@
       <c r="R38" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S38" s="141" t="s">
+      <c r="S38" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T38" s="141" t="s">
+      <c r="T38" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U38" s="144" t="s">
+      <c r="U38" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V38" s="108"/>
@@ -27020,9 +27022,9 @@
       <c r="R39" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S39" s="142"/>
-      <c r="T39" s="142"/>
-      <c r="U39" s="142"/>
+      <c r="S39" s="161"/>
+      <c r="T39" s="161"/>
+      <c r="U39" s="161"/>
       <c r="V39" s="108"/>
       <c r="W39" s="99" t="s">
         <v>43</v>
@@ -27112,9 +27114,9 @@
       <c r="R40" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S40" s="143"/>
-      <c r="T40" s="143"/>
-      <c r="U40" s="143"/>
+      <c r="S40" s="152"/>
+      <c r="T40" s="152"/>
+      <c r="U40" s="152"/>
       <c r="V40" s="108"/>
       <c r="W40" s="99" t="s">
         <v>43</v>
@@ -27472,13 +27474,13 @@
       <c r="R45" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S45" s="141" t="s">
+      <c r="S45" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T45" s="141" t="s">
+      <c r="T45" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U45" s="144" t="s">
+      <c r="U45" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V45" s="108"/>
@@ -27570,9 +27572,9 @@
       <c r="R46" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S46" s="142"/>
-      <c r="T46" s="142"/>
-      <c r="U46" s="142"/>
+      <c r="S46" s="161"/>
+      <c r="T46" s="161"/>
+      <c r="U46" s="161"/>
       <c r="V46" s="108"/>
       <c r="W46" s="99" t="s">
         <v>43</v>
@@ -27662,9 +27664,9 @@
       <c r="R47" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S47" s="143"/>
-      <c r="T47" s="143"/>
-      <c r="U47" s="143"/>
+      <c r="S47" s="152"/>
+      <c r="T47" s="152"/>
+      <c r="U47" s="152"/>
       <c r="V47" s="108"/>
       <c r="W47" s="99" t="s">
         <v>43</v>
@@ -28030,13 +28032,13 @@
       <c r="R52" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S52" s="141" t="s">
+      <c r="S52" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T52" s="141" t="s">
+      <c r="T52" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="144" t="s">
+      <c r="U52" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V52" s="108"/>
@@ -28128,9 +28130,9 @@
       <c r="R53" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S53" s="142"/>
-      <c r="T53" s="142"/>
-      <c r="U53" s="142"/>
+      <c r="S53" s="161"/>
+      <c r="T53" s="161"/>
+      <c r="U53" s="161"/>
       <c r="V53" s="108"/>
       <c r="W53" s="99" t="s">
         <v>43</v>
@@ -28220,9 +28222,9 @@
       <c r="R54" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S54" s="143"/>
-      <c r="T54" s="143"/>
-      <c r="U54" s="143"/>
+      <c r="S54" s="152"/>
+      <c r="T54" s="152"/>
+      <c r="U54" s="152"/>
       <c r="V54" s="108"/>
       <c r="W54" s="99" t="s">
         <v>43</v>
@@ -28446,13 +28448,13 @@
       <c r="R57" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S57" s="141" t="s">
+      <c r="S57" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T57" s="141" t="s">
+      <c r="T57" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="144" t="s">
+      <c r="U57" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="108"/>
@@ -28544,9 +28546,9 @@
       <c r="R58" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S58" s="142"/>
-      <c r="T58" s="142"/>
-      <c r="U58" s="142"/>
+      <c r="S58" s="161"/>
+      <c r="T58" s="161"/>
+      <c r="U58" s="161"/>
       <c r="V58" s="108"/>
       <c r="W58" s="99" t="s">
         <v>43</v>
@@ -28636,9 +28638,9 @@
       <c r="R59" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S59" s="143"/>
-      <c r="T59" s="143"/>
-      <c r="U59" s="143"/>
+      <c r="S59" s="152"/>
+      <c r="T59" s="152"/>
+      <c r="U59" s="152"/>
       <c r="V59" s="108"/>
       <c r="W59" s="99" t="s">
         <v>43</v>
@@ -28864,13 +28866,13 @@
       <c r="R62" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S62" s="141" t="s">
+      <c r="S62" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T62" s="141" t="s">
+      <c r="T62" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U62" s="144" t="s">
+      <c r="U62" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V62" s="108"/>
@@ -28962,9 +28964,9 @@
       <c r="R63" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S63" s="142"/>
-      <c r="T63" s="142"/>
-      <c r="U63" s="142"/>
+      <c r="S63" s="161"/>
+      <c r="T63" s="161"/>
+      <c r="U63" s="161"/>
       <c r="V63" s="108"/>
       <c r="W63" s="99" t="s">
         <v>43</v>
@@ -29054,9 +29056,9 @@
       <c r="R64" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S64" s="143"/>
-      <c r="T64" s="143"/>
-      <c r="U64" s="143"/>
+      <c r="S64" s="152"/>
+      <c r="T64" s="152"/>
+      <c r="U64" s="152"/>
       <c r="V64" s="108"/>
       <c r="W64" s="99" t="s">
         <v>43</v>
@@ -29275,13 +29277,13 @@
       <c r="R67" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S67" s="141" t="s">
+      <c r="S67" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T67" s="141" t="s">
+      <c r="T67" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U67" s="144" t="s">
+      <c r="U67" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V67" s="108"/>
@@ -29373,9 +29375,9 @@
       <c r="R68" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S68" s="142"/>
-      <c r="T68" s="142"/>
-      <c r="U68" s="142"/>
+      <c r="S68" s="161"/>
+      <c r="T68" s="161"/>
+      <c r="U68" s="161"/>
       <c r="V68" s="108"/>
       <c r="W68" s="99" t="s">
         <v>43</v>
@@ -29465,9 +29467,9 @@
       <c r="R69" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S69" s="143"/>
-      <c r="T69" s="143"/>
-      <c r="U69" s="143"/>
+      <c r="S69" s="152"/>
+      <c r="T69" s="152"/>
+      <c r="U69" s="152"/>
       <c r="V69" s="108"/>
       <c r="W69" s="99" t="s">
         <v>43</v>
@@ -29825,13 +29827,13 @@
       <c r="R74" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S74" s="141" t="s">
+      <c r="S74" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="T74" s="141" t="s">
+      <c r="T74" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U74" s="144" t="s">
+      <c r="U74" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V74" s="108"/>
@@ -29923,9 +29925,9 @@
       <c r="R75" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S75" s="142"/>
-      <c r="T75" s="142"/>
-      <c r="U75" s="142"/>
+      <c r="S75" s="161"/>
+      <c r="T75" s="161"/>
+      <c r="U75" s="161"/>
       <c r="V75" s="108"/>
       <c r="W75" s="99" t="s">
         <v>43</v>
@@ -30015,9 +30017,9 @@
       <c r="R76" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S76" s="143"/>
-      <c r="T76" s="143"/>
-      <c r="U76" s="143"/>
+      <c r="S76" s="152"/>
+      <c r="T76" s="152"/>
+      <c r="U76" s="152"/>
       <c r="V76" s="108"/>
       <c r="W76" s="99" t="s">
         <v>43</v>
@@ -30236,13 +30238,13 @@
       <c r="R79" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S79" s="141" t="s">
+      <c r="S79" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="T79" s="141" t="s">
+      <c r="T79" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U79" s="144" t="s">
+      <c r="U79" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V79" s="108"/>
@@ -30334,9 +30336,9 @@
       <c r="R80" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S80" s="142"/>
-      <c r="T80" s="142"/>
-      <c r="U80" s="142"/>
+      <c r="S80" s="161"/>
+      <c r="T80" s="161"/>
+      <c r="U80" s="161"/>
       <c r="V80" s="108"/>
       <c r="W80" s="99" t="s">
         <v>43</v>
@@ -30426,9 +30428,9 @@
       <c r="R81" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S81" s="143"/>
-      <c r="T81" s="143"/>
-      <c r="U81" s="143"/>
+      <c r="S81" s="152"/>
+      <c r="T81" s="152"/>
+      <c r="U81" s="152"/>
       <c r="V81" s="108"/>
       <c r="W81" s="99" t="s">
         <v>43</v>
@@ -30799,13 +30801,13 @@
       <c r="R86" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S86" s="141" t="s">
+      <c r="S86" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="T86" s="141" t="s">
+      <c r="T86" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U86" s="144" t="s">
+      <c r="U86" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V86" s="108"/>
@@ -30897,9 +30899,9 @@
       <c r="R87" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S87" s="142"/>
-      <c r="T87" s="142"/>
-      <c r="U87" s="142"/>
+      <c r="S87" s="161"/>
+      <c r="T87" s="161"/>
+      <c r="U87" s="161"/>
       <c r="V87" s="108"/>
       <c r="W87" s="99" t="s">
         <v>43</v>
@@ -30989,9 +30991,9 @@
       <c r="R88" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S88" s="143"/>
-      <c r="T88" s="143"/>
-      <c r="U88" s="143"/>
+      <c r="S88" s="152"/>
+      <c r="T88" s="152"/>
+      <c r="U88" s="152"/>
       <c r="V88" s="108"/>
       <c r="W88" s="99" t="s">
         <v>43</v>
@@ -31358,13 +31360,13 @@
       <c r="R93" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S93" s="141" t="s">
+      <c r="S93" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T93" s="141" t="s">
+      <c r="T93" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U93" s="144" t="s">
+      <c r="U93" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V93" s="108"/>
@@ -31456,9 +31458,9 @@
       <c r="R94" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S94" s="142"/>
-      <c r="T94" s="142"/>
-      <c r="U94" s="142"/>
+      <c r="S94" s="161"/>
+      <c r="T94" s="161"/>
+      <c r="U94" s="161"/>
       <c r="V94" s="108"/>
       <c r="W94" s="99" t="s">
         <v>43</v>
@@ -31548,9 +31550,9 @@
       <c r="R95" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S95" s="143"/>
-      <c r="T95" s="143"/>
-      <c r="U95" s="143"/>
+      <c r="S95" s="152"/>
+      <c r="T95" s="152"/>
+      <c r="U95" s="152"/>
       <c r="V95" s="108"/>
       <c r="W95" s="99" t="s">
         <v>43</v>
@@ -31769,13 +31771,13 @@
       <c r="R98" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S98" s="141" t="s">
+      <c r="S98" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T98" s="141" t="s">
+      <c r="T98" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U98" s="144" t="s">
+      <c r="U98" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V98" s="108"/>
@@ -31867,9 +31869,9 @@
       <c r="R99" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S99" s="142"/>
-      <c r="T99" s="142"/>
-      <c r="U99" s="142"/>
+      <c r="S99" s="161"/>
+      <c r="T99" s="161"/>
+      <c r="U99" s="161"/>
       <c r="V99" s="108"/>
       <c r="W99" s="99" t="s">
         <v>43</v>
@@ -31959,9 +31961,9 @@
       <c r="R100" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S100" s="143"/>
-      <c r="T100" s="143"/>
-      <c r="U100" s="143"/>
+      <c r="S100" s="152"/>
+      <c r="T100" s="152"/>
+      <c r="U100" s="152"/>
       <c r="V100" s="108"/>
       <c r="W100" s="99" t="s">
         <v>43</v>
@@ -32340,13 +32342,13 @@
       <c r="R105" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S105" s="141" t="s">
+      <c r="S105" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T105" s="141" t="s">
+      <c r="T105" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U105" s="144" t="s">
+      <c r="U105" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V105" s="108"/>
@@ -32445,9 +32447,9 @@
       <c r="R106" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S106" s="142"/>
-      <c r="T106" s="142"/>
-      <c r="U106" s="142"/>
+      <c r="S106" s="161"/>
+      <c r="T106" s="161"/>
+      <c r="U106" s="161"/>
       <c r="V106" s="108"/>
       <c r="W106" s="99" t="s">
         <v>43</v>
@@ -32537,9 +32539,9 @@
       <c r="R107" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S107" s="143"/>
-      <c r="T107" s="143"/>
-      <c r="U107" s="143"/>
+      <c r="S107" s="152"/>
+      <c r="T107" s="152"/>
+      <c r="U107" s="152"/>
       <c r="V107" s="108"/>
       <c r="W107" s="99" t="s">
         <v>43</v>
@@ -32911,13 +32913,13 @@
       <c r="R112" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S112" s="141" t="s">
+      <c r="S112" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="T112" s="141" t="s">
+      <c r="T112" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U112" s="144" t="s">
+      <c r="U112" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V112" s="108"/>
@@ -33009,9 +33011,9 @@
       <c r="R113" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S113" s="142"/>
-      <c r="T113" s="142"/>
-      <c r="U113" s="142"/>
+      <c r="S113" s="161"/>
+      <c r="T113" s="161"/>
+      <c r="U113" s="161"/>
       <c r="V113" s="108"/>
       <c r="W113" s="99" t="s">
         <v>43</v>
@@ -33101,9 +33103,9 @@
       <c r="R114" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S114" s="143"/>
-      <c r="T114" s="143"/>
-      <c r="U114" s="143"/>
+      <c r="S114" s="152"/>
+      <c r="T114" s="152"/>
+      <c r="U114" s="152"/>
       <c r="V114" s="108"/>
       <c r="W114" s="99" t="s">
         <v>43</v>
@@ -33335,13 +33337,13 @@
       <c r="R117" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S117" s="141" t="s">
+      <c r="S117" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T117" s="141" t="s">
+      <c r="T117" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U117" s="144" t="s">
+      <c r="U117" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V117" s="108"/>
@@ -33440,9 +33442,9 @@
       <c r="R118" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S118" s="142"/>
-      <c r="T118" s="142"/>
-      <c r="U118" s="142"/>
+      <c r="S118" s="161"/>
+      <c r="T118" s="161"/>
+      <c r="U118" s="161"/>
       <c r="V118" s="108"/>
       <c r="W118" s="99" t="s">
         <v>43</v>
@@ -33539,9 +33541,9 @@
       <c r="R119" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S119" s="143"/>
-      <c r="T119" s="143"/>
-      <c r="U119" s="143"/>
+      <c r="S119" s="152"/>
+      <c r="T119" s="152"/>
+      <c r="U119" s="152"/>
       <c r="V119" s="108"/>
       <c r="W119" s="99" t="s">
         <v>43</v>
@@ -33774,13 +33776,13 @@
       <c r="R122" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S122" s="141" t="s">
+      <c r="S122" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T122" s="141" t="s">
+      <c r="T122" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U122" s="144" t="s">
+      <c r="U122" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V122" s="108"/>
@@ -33872,9 +33874,9 @@
       <c r="R123" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S123" s="142"/>
-      <c r="T123" s="142"/>
-      <c r="U123" s="142"/>
+      <c r="S123" s="161"/>
+      <c r="T123" s="161"/>
+      <c r="U123" s="161"/>
       <c r="V123" s="108"/>
       <c r="W123" s="99" t="s">
         <v>43</v>
@@ -33964,9 +33966,9 @@
       <c r="R124" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S124" s="143"/>
-      <c r="T124" s="143"/>
-      <c r="U124" s="143"/>
+      <c r="S124" s="152"/>
+      <c r="T124" s="152"/>
+      <c r="U124" s="152"/>
       <c r="V124" s="108"/>
       <c r="W124" s="99" t="s">
         <v>43</v>
@@ -34185,13 +34187,13 @@
       <c r="R127" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S127" s="141" t="s">
+      <c r="S127" s="160" t="s">
         <v>578</v>
       </c>
-      <c r="T127" s="141" t="s">
+      <c r="T127" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U127" s="144" t="s">
+      <c r="U127" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V127" s="108"/>
@@ -34283,9 +34285,9 @@
       <c r="R128" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S128" s="142"/>
-      <c r="T128" s="142"/>
-      <c r="U128" s="142"/>
+      <c r="S128" s="161"/>
+      <c r="T128" s="161"/>
+      <c r="U128" s="161"/>
       <c r="V128" s="108"/>
       <c r="W128" s="99" t="s">
         <v>43</v>
@@ -34375,9 +34377,9 @@
       <c r="R129" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="S129" s="143"/>
-      <c r="T129" s="143"/>
-      <c r="U129" s="143"/>
+      <c r="S129" s="152"/>
+      <c r="T129" s="152"/>
+      <c r="U129" s="152"/>
       <c r="V129" s="108"/>
       <c r="W129" s="99" t="s">
         <v>43</v>
@@ -41608,10 +41610,10 @@
       <c r="R225" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S225" s="146" t="s">
+      <c r="S225" s="162" t="s">
         <v>342</v>
       </c>
-      <c r="T225" s="146" t="s">
+      <c r="T225" s="162" t="s">
         <v>343</v>
       </c>
       <c r="U225" s="108"/>
@@ -41694,8 +41696,8 @@
       <c r="R226" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S226" s="142"/>
-      <c r="T226" s="142"/>
+      <c r="S226" s="161"/>
+      <c r="T226" s="161"/>
       <c r="U226" s="108"/>
       <c r="V226" s="108"/>
       <c r="W226" s="99" t="s">
@@ -41783,8 +41785,8 @@
       <c r="R227" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S227" s="142"/>
-      <c r="T227" s="142"/>
+      <c r="S227" s="161"/>
+      <c r="T227" s="161"/>
       <c r="U227" s="108"/>
       <c r="V227" s="108"/>
       <c r="W227" s="99" t="s">
@@ -41872,8 +41874,8 @@
       <c r="R228" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S228" s="142"/>
-      <c r="T228" s="142"/>
+      <c r="S228" s="161"/>
+      <c r="T228" s="161"/>
       <c r="U228" s="108"/>
       <c r="V228" s="108"/>
       <c r="W228" s="99" t="s">
@@ -41954,8 +41956,8 @@
       <c r="R229" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S229" s="142"/>
-      <c r="T229" s="142"/>
+      <c r="S229" s="161"/>
+      <c r="T229" s="161"/>
       <c r="U229" s="108"/>
       <c r="V229" s="108"/>
       <c r="W229" s="99" t="s">
@@ -42036,8 +42038,8 @@
       <c r="R230" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S230" s="143"/>
-      <c r="T230" s="143"/>
+      <c r="S230" s="152"/>
+      <c r="T230" s="152"/>
       <c r="U230" s="108"/>
       <c r="V230" s="108"/>
       <c r="W230" s="99" t="s">
@@ -42796,7 +42798,7 @@
       <c r="R242" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="S242" s="141" t="s">
+      <c r="S242" s="160" t="s">
         <v>318</v>
       </c>
       <c r="T242" s="104"/>
@@ -42854,7 +42856,7 @@
       <c r="R243" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="S243" s="142"/>
+      <c r="S243" s="161"/>
       <c r="T243" s="104"/>
       <c r="U243" s="104"/>
       <c r="V243" s="104"/>
@@ -42918,7 +42920,7 @@
       <c r="R244" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="S244" s="142"/>
+      <c r="S244" s="161"/>
       <c r="T244" s="108"/>
       <c r="U244" s="108"/>
       <c r="V244" s="108"/>
@@ -42975,7 +42977,7 @@
       <c r="R245" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="S245" s="143"/>
+      <c r="S245" s="152"/>
       <c r="T245" s="108"/>
       <c r="U245" s="108"/>
       <c r="V245" s="108"/>
@@ -44380,21 +44382,45 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="S225:S230"/>
-    <mergeCell ref="S122:S124"/>
-    <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="U62:U64"/>
-    <mergeCell ref="T117:T119"/>
-    <mergeCell ref="S112:S114"/>
-    <mergeCell ref="S57:S59"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="U28:U30"/>
-    <mergeCell ref="U93:U95"/>
-    <mergeCell ref="S127:S129"/>
-    <mergeCell ref="T225:T230"/>
-    <mergeCell ref="S74:S76"/>
+    <mergeCell ref="S242:S245"/>
+    <mergeCell ref="U33:U35"/>
+    <mergeCell ref="U98:U100"/>
+    <mergeCell ref="U67:U69"/>
+    <mergeCell ref="U117:U119"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="U79:U81"/>
+    <mergeCell ref="U38:U40"/>
+    <mergeCell ref="U112:U114"/>
+    <mergeCell ref="T122:T124"/>
+    <mergeCell ref="S67:S69"/>
+    <mergeCell ref="T67:T69"/>
+    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S18:S20"/>
+    <mergeCell ref="U122:U124"/>
+    <mergeCell ref="U18:U20"/>
+    <mergeCell ref="T79:T81"/>
+    <mergeCell ref="U127:U129"/>
+    <mergeCell ref="U23:U25"/>
+    <mergeCell ref="T105:T107"/>
+    <mergeCell ref="T52:T54"/>
+    <mergeCell ref="T86:T88"/>
+    <mergeCell ref="S93:S95"/>
+    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="S33:S35"/>
+    <mergeCell ref="T23:T25"/>
+    <mergeCell ref="T28:T30"/>
+    <mergeCell ref="S45:S47"/>
+    <mergeCell ref="S79:S81"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T33:T35"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="T98:T100"/>
+    <mergeCell ref="T45:T47"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="S11:S13"/>
     <mergeCell ref="T74:T76"/>
     <mergeCell ref="T112:T114"/>
@@ -44411,45 +44437,21 @@
     <mergeCell ref="S52:S54"/>
     <mergeCell ref="S86:S88"/>
     <mergeCell ref="U86:U88"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T33:T35"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="T98:T100"/>
-    <mergeCell ref="T45:T47"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="S18:S20"/>
-    <mergeCell ref="U122:U124"/>
-    <mergeCell ref="U18:U20"/>
-    <mergeCell ref="T79:T81"/>
-    <mergeCell ref="U127:U129"/>
-    <mergeCell ref="U23:U25"/>
-    <mergeCell ref="T105:T107"/>
-    <mergeCell ref="T52:T54"/>
-    <mergeCell ref="T86:T88"/>
-    <mergeCell ref="S93:S95"/>
-    <mergeCell ref="S62:S64"/>
-    <mergeCell ref="S33:S35"/>
-    <mergeCell ref="T23:T25"/>
-    <mergeCell ref="T28:T30"/>
-    <mergeCell ref="S45:S47"/>
-    <mergeCell ref="S79:S81"/>
-    <mergeCell ref="S242:S245"/>
-    <mergeCell ref="U33:U35"/>
-    <mergeCell ref="U98:U100"/>
-    <mergeCell ref="U67:U69"/>
-    <mergeCell ref="U117:U119"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="U79:U81"/>
-    <mergeCell ref="U38:U40"/>
-    <mergeCell ref="U112:U114"/>
-    <mergeCell ref="T122:T124"/>
-    <mergeCell ref="S67:S69"/>
-    <mergeCell ref="T67:T69"/>
-    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="S225:S230"/>
+    <mergeCell ref="S122:S124"/>
+    <mergeCell ref="U57:U59"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="U62:U64"/>
+    <mergeCell ref="T117:T119"/>
+    <mergeCell ref="S112:S114"/>
+    <mergeCell ref="S57:S59"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="U28:U30"/>
+    <mergeCell ref="U93:U95"/>
+    <mergeCell ref="S127:S129"/>
+    <mergeCell ref="T225:T230"/>
+    <mergeCell ref="S74:S76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cost/Cost_Database.xlsx
+++ b/cost/Cost_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannbn/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A49C757-241D-224B-8625-BF8CFCE3D588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79ED3FA-4632-4E49-813F-E19768611E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="877" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2251,10 +2251,10 @@
     <t>Moderator Booster Mass Graphite</t>
   </si>
   <si>
-    <t>Moderator Booster Mass Yhx</t>
-  </si>
-  <si>
     <t>Moderator Booster Mass ZrH</t>
+  </si>
+  <si>
+    <t>Moderator Booster Mass YHx</t>
   </si>
 </sst>
 </file>
@@ -2961,21 +2961,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2983,8 +2983,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3009,14 +3009,14 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3026,7 +3026,7 @@
     <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Normal 2 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="324">
+  <dxfs count="302">
     <dxf>
       <fill>
         <patternFill>
@@ -3052,6 +3052,230 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3086,7 +3310,104 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3108,6 +3429,100 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3161,20 +3576,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -3190,6 +3591,109 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3271,78 +3775,20 @@
     <dxf>
       <font>
         <b/>
+        <i/>
       </font>
-    </dxf>
-    <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
+        <patternFill patternType="gray125"/>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
+        <i/>
       </font>
-    </dxf>
-    <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
+        <patternFill patternType="gray0625"/>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -3371,43 +3817,12 @@
       </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
+        <i/>
       </font>
-    </dxf>
-    <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
+        <patternFill patternType="gray125"/>
       </fill>
     </dxf>
     <dxf>
@@ -3453,128 +3868,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
+        <i/>
       </font>
-    </dxf>
-    <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
+        <patternFill patternType="gray125"/>
       </fill>
     </dxf>
     <dxf>
@@ -3601,161 +3900,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -3771,316 +3915,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4144,9 +3978,79 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4191,9 +4095,11 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4202,27 +4108,6 @@
       </font>
       <fill>
         <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -4243,6 +4128,83 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray0625"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray125"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray0625"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4275,22 +4237,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFBA"/>
@@ -4298,109 +4244,9 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray125"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -4429,9 +4275,63 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -4478,6 +4378,88 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -4497,9 +4479,25 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4524,6 +4522,99 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray0625"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="gray0625"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4612,11 +4703,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -4645,18 +4731,14 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4680,26 +4762,10 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
       <fill>
-        <patternFill patternType="gray0625"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="gray0625"/>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -4745,149 +4811,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
@@ -4909,14 +4832,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4924,34 +4840,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4982,79 +4870,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
       </font>
@@ -5072,6 +4887,39 @@
           <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFBA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -5114,14 +4962,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFBA"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5131,6 +4979,11 @@
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -5152,11 +5005,6 @@
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -5207,6 +5055,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFBA"/>
         </patternFill>
       </fill>
@@ -5215,13 +5070,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5779,7 +5627,7 @@
       <c r="S3" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="141" t="s">
+      <c r="T3" s="145" t="s">
         <v>41</v>
       </c>
       <c r="U3" s="148" t="s">
@@ -6404,13 +6252,13 @@
       <c r="R11" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="S11" s="141" t="s">
+      <c r="S11" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="141" t="s">
+      <c r="T11" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="146" t="s">
+      <c r="U11" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="49"/>
@@ -6727,13 +6575,13 @@
       <c r="R15" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S15" s="141" t="s">
+      <c r="S15" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T15" s="141" t="s">
+      <c r="T15" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U15" s="146" t="s">
+      <c r="U15" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V15" s="49"/>
@@ -7273,13 +7121,13 @@
       <c r="R22" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S22" s="141" t="s">
+      <c r="S22" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T22" s="141" t="s">
+      <c r="T22" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U22" s="146" t="s">
+      <c r="U22" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V22" s="49"/>
@@ -7582,13 +7430,13 @@
       <c r="R26" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S26" s="141" t="s">
+      <c r="S26" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T26" s="141" t="s">
+      <c r="T26" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U26" s="146" t="s">
+      <c r="U26" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V26" s="49"/>
@@ -7899,13 +7747,13 @@
       <c r="R30" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S30" s="141" t="s">
+      <c r="S30" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T30" s="141" t="s">
+      <c r="T30" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U30" s="146" t="s">
+      <c r="U30" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V30" s="49"/>
@@ -8406,13 +8254,13 @@
       <c r="R37" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S37" s="141" t="s">
+      <c r="S37" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T37" s="141" t="s">
+      <c r="T37" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U37" s="146" t="s">
+      <c r="U37" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V37" s="49"/>
@@ -8713,13 +8561,13 @@
       <c r="R41" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S41" s="141" t="s">
+      <c r="S41" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="141" t="s">
+      <c r="T41" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U41" s="146" t="s">
+      <c r="U41" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V41" s="49"/>
@@ -9074,13 +8922,13 @@
       <c r="R46" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S46" s="141" t="s">
+      <c r="S46" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T46" s="141" t="s">
+      <c r="T46" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U46" s="146" t="s">
+      <c r="U46" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V46" s="49"/>
@@ -9525,16 +9373,16 @@
       <c r="R52" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="S52" s="141" t="s">
+      <c r="S52" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T52" s="141" t="s">
+      <c r="T52" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="146" t="s">
+      <c r="U52" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="V52" s="147" t="s">
+      <c r="V52" s="150" t="s">
         <v>162</v>
       </c>
       <c r="W52" s="77" t="s">
@@ -9881,13 +9729,13 @@
       <c r="R57" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S57" s="141" t="s">
+      <c r="S57" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="T57" s="141" t="s">
+      <c r="T57" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="146" t="s">
+      <c r="U57" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="49"/>
@@ -10190,13 +10038,13 @@
       <c r="R61" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="S61" s="141" t="s">
+      <c r="S61" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="T61" s="141" t="s">
+      <c r="T61" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="U61" s="146" t="s">
+      <c r="U61" s="144" t="s">
         <v>76</v>
       </c>
       <c r="V61" s="49"/>
@@ -10694,7 +10542,7 @@
       <c r="S68" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="T68" s="144" t="s">
+      <c r="T68" s="146" t="s">
         <v>197</v>
       </c>
       <c r="U68" s="56"/>
@@ -11375,10 +11223,10 @@
       <c r="S76" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="T76" s="144" t="s">
+      <c r="T76" s="146" t="s">
         <v>210</v>
       </c>
-      <c r="U76" s="150" t="s">
+      <c r="U76" s="147" t="s">
         <v>211</v>
       </c>
       <c r="V76" s="59" t="s">
@@ -12293,7 +12141,7 @@
       <c r="T86" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="U86" s="150" t="s">
+      <c r="U86" s="147" t="s">
         <v>211</v>
       </c>
       <c r="V86" s="49"/>
@@ -13731,7 +13579,7 @@
         <v>186</v>
       </c>
       <c r="M102" s="59" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O102" s="49" t="s">
         <v>188</v>
@@ -13816,7 +13664,7 @@
         <v>186</v>
       </c>
       <c r="M103" s="59" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O103" s="49" t="s">
         <v>188</v>
@@ -14025,13 +13873,13 @@
       <c r="S106" s="59" t="s">
         <v>268</v>
       </c>
-      <c r="T106" s="144" t="s">
+      <c r="T106" s="146" t="s">
         <v>269</v>
       </c>
       <c r="U106" s="149" t="s">
         <v>270</v>
       </c>
-      <c r="V106" s="144"/>
+      <c r="V106" s="146"/>
       <c r="W106" s="77" t="s">
         <v>157</v>
       </c>
@@ -15316,7 +15164,7 @@
         <v>292</v>
       </c>
       <c r="U120" s="83"/>
-      <c r="V120" s="144" t="s">
+      <c r="V120" s="146" t="s">
         <v>307</v>
       </c>
       <c r="W120" s="77" t="s">
@@ -16436,10 +16284,10 @@
       <c r="R135" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="S135" s="145" t="s">
+      <c r="S135" s="141" t="s">
         <v>340</v>
       </c>
-      <c r="T135" s="145" t="s">
+      <c r="T135" s="141" t="s">
         <v>341</v>
       </c>
       <c r="U135" s="49"/>
@@ -17006,10 +16854,10 @@
       <c r="R142" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="S142" s="144" t="s">
+      <c r="S142" s="146" t="s">
         <v>350</v>
       </c>
-      <c r="T142" s="144" t="s">
+      <c r="T142" s="146" t="s">
         <v>351</v>
       </c>
       <c r="U142" s="49"/>
@@ -17778,7 +17626,7 @@
       <c r="R152" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="S152" s="141" t="s">
+      <c r="S152" s="145" t="s">
         <v>316</v>
       </c>
       <c r="T152" s="46"/>
@@ -19034,14 +18882,14 @@
       <c r="P170" s="49"/>
       <c r="Q170" s="66"/>
       <c r="R170" s="49"/>
-      <c r="S170" s="144" t="s">
+      <c r="S170" s="146" t="s">
         <v>399</v>
       </c>
-      <c r="T170" s="144" t="s">
+      <c r="T170" s="146" t="s">
         <v>399</v>
       </c>
       <c r="U170" s="49"/>
-      <c r="V170" s="144" t="s">
+      <c r="V170" s="146" t="s">
         <v>400</v>
       </c>
       <c r="W170" s="77"/>
@@ -19673,6 +19521,43 @@
   </sheetData>
   <autoFilter ref="A1:AB181" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="53">
+    <mergeCell ref="T26:T28"/>
+    <mergeCell ref="T41:T43"/>
+    <mergeCell ref="V106:V107"/>
+    <mergeCell ref="T61:T63"/>
+    <mergeCell ref="T76:T80"/>
+    <mergeCell ref="S135:S140"/>
+    <mergeCell ref="T11:T13"/>
+    <mergeCell ref="V170:V176"/>
+    <mergeCell ref="S30:S32"/>
+    <mergeCell ref="S15:S17"/>
+    <mergeCell ref="T37:T39"/>
+    <mergeCell ref="T46:T48"/>
+    <mergeCell ref="T22:T24"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="S26:S28"/>
+    <mergeCell ref="U26:U28"/>
+    <mergeCell ref="T52:T54"/>
+    <mergeCell ref="V120:V121"/>
+    <mergeCell ref="S152:S155"/>
+    <mergeCell ref="T142:T147"/>
+    <mergeCell ref="V52:V54"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="S41:S43"/>
+    <mergeCell ref="U106:U107"/>
+    <mergeCell ref="T68:T73"/>
+    <mergeCell ref="S46:S48"/>
+    <mergeCell ref="S22:S24"/>
+    <mergeCell ref="U22:U24"/>
+    <mergeCell ref="T30:T32"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="U11:U13"/>
+    <mergeCell ref="U37:U39"/>
+    <mergeCell ref="T106:T107"/>
     <mergeCell ref="T135:T140"/>
     <mergeCell ref="U30:U32"/>
     <mergeCell ref="S52:S54"/>
@@ -19689,331 +19574,294 @@
     <mergeCell ref="S57:S59"/>
     <mergeCell ref="S37:S39"/>
     <mergeCell ref="U86:U96"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T15:T17"/>
-    <mergeCell ref="S41:S43"/>
-    <mergeCell ref="U106:U107"/>
-    <mergeCell ref="T68:T73"/>
-    <mergeCell ref="S46:S48"/>
-    <mergeCell ref="S22:S24"/>
-    <mergeCell ref="U22:U24"/>
-    <mergeCell ref="T30:T32"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="U11:U13"/>
-    <mergeCell ref="U37:U39"/>
-    <mergeCell ref="T106:T107"/>
-    <mergeCell ref="S135:S140"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="V170:V176"/>
-    <mergeCell ref="S30:S32"/>
-    <mergeCell ref="S15:S17"/>
-    <mergeCell ref="T37:T39"/>
-    <mergeCell ref="T46:T48"/>
-    <mergeCell ref="T22:T24"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="S26:S28"/>
-    <mergeCell ref="U26:U28"/>
-    <mergeCell ref="T52:T54"/>
-    <mergeCell ref="V120:V121"/>
-    <mergeCell ref="S152:S155"/>
-    <mergeCell ref="T142:T147"/>
-    <mergeCell ref="V52:V54"/>
-    <mergeCell ref="T26:T28"/>
-    <mergeCell ref="T41:T43"/>
-    <mergeCell ref="V106:V107"/>
-    <mergeCell ref="T61:T63"/>
-    <mergeCell ref="T76:T80"/>
   </mergeCells>
   <conditionalFormatting sqref="A97:B103">
-    <cfRule type="expression" dxfId="323" priority="572">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="322" priority="574">
+    <cfRule type="expression" dxfId="301" priority="574">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="321" priority="573">
+    <cfRule type="expression" dxfId="300" priority="573">
       <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="299" priority="572">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106:F108 U113:V119 U120:U121 A135:B140 N142:V142 N143:R143 U143:V148 K144:R144 A148:T148 T152:V157 A158:V161 A162:J163">
-    <cfRule type="expression" dxfId="320" priority="788">
+    <cfRule type="expression" dxfId="298" priority="788">
       <formula>$B106=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A97:I103">
-    <cfRule type="expression" dxfId="319" priority="35">
+    <cfRule type="expression" dxfId="297" priority="35">
       <formula>$B97=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A147:R147">
-    <cfRule type="expression" dxfId="318" priority="736">
+    <cfRule type="expression" dxfId="296" priority="736">
       <formula>$B147=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A150:R157">
-    <cfRule type="expression" dxfId="317" priority="682">
+    <cfRule type="expression" dxfId="295" priority="682">
       <formula>$B150=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="316" priority="681">
+    <cfRule type="expression" dxfId="294" priority="681">
       <formula>$B150=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="315" priority="684">
+    <cfRule type="expression" dxfId="293" priority="684">
       <formula>$B150=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="314" priority="683">
+    <cfRule type="expression" dxfId="292" priority="683">
       <formula>$B150&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A124:S125 U124:V125 U166:V168">
-    <cfRule type="expression" dxfId="313" priority="581">
+    <cfRule type="expression" dxfId="291" priority="581">
       <formula>$B124=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:U105">
-    <cfRule type="expression" dxfId="312" priority="792">
-      <formula>$B105=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="311" priority="790">
+    <cfRule type="expression" dxfId="290" priority="790">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="310" priority="789">
+    <cfRule type="expression" dxfId="289" priority="789">
       <formula>$B105=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="309" priority="791">
+    <cfRule type="expression" dxfId="288" priority="791">
       <formula>$B105&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="287" priority="792">
+      <formula>$B105=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74:V96 A104:V104 A170:R176">
-    <cfRule type="expression" dxfId="308" priority="488">
+    <cfRule type="expression" dxfId="286" priority="488">
       <formula>$B74&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="307" priority="487">
+    <cfRule type="expression" dxfId="285" priority="486">
+      <formula>$B74=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="284" priority="487">
       <formula>$B74=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="306" priority="486">
-      <formula>$B74=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:V83">
-    <cfRule type="expression" dxfId="305" priority="576">
+    <cfRule type="expression" dxfId="283" priority="576">
       <formula>$B76=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A95:V96 D97:D103 A122:V123 A126:V140 A141:AG144 A145:G146 I145:AG146 A147:AG169">
-    <cfRule type="expression" dxfId="304" priority="621">
+    <cfRule type="expression" dxfId="282" priority="621">
       <formula>$B95&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109:V111 U113:V119 U120:U121 A124:S125 U124:V125 A141:AG144 A145:G146 I145:AG146 A147:AG169 A135:B140 U135:V140 U143:V148 A5:S6 A106:F108 A1:AG4 U5:AG6">
-    <cfRule type="expression" dxfId="303" priority="785">
+    <cfRule type="expression" dxfId="281" priority="785">
       <formula>$B1=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122:V123 A126:V140 A95:V96 D97:D103 A141:AG144 A145:G146 I145:AG146 A147:AG169">
-    <cfRule type="expression" dxfId="302" priority="620">
+    <cfRule type="expression" dxfId="280" priority="620">
       <formula>$B95=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122:V123">
-    <cfRule type="expression" dxfId="301" priority="756">
+    <cfRule type="expression" dxfId="279" priority="756">
       <formula>$B122=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:V140 A122:V123">
-    <cfRule type="expression" dxfId="300" priority="619">
+    <cfRule type="expression" dxfId="278" priority="619">
       <formula>$B122=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A149:V149">
-    <cfRule type="expression" dxfId="299" priority="717">
-      <formula>$B149=3</formula>
+    <cfRule type="expression" dxfId="277" priority="720">
+      <formula>$B149=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="298" priority="718">
+    <cfRule type="expression" dxfId="276" priority="719">
+      <formula>$B149&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="275" priority="718">
       <formula>$B149=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="297" priority="720">
-      <formula>$B149=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="296" priority="719">
-      <formula>$B149&lt;2</formula>
+    <cfRule type="expression" dxfId="274" priority="717">
+      <formula>$B149=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178:V181">
-    <cfRule type="expression" dxfId="295" priority="652">
-      <formula>$B178=0</formula>
+    <cfRule type="expression" dxfId="273" priority="651">
+      <formula>$B178&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="294" priority="649">
+    <cfRule type="expression" dxfId="272" priority="649">
       <formula>$B178=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="293" priority="650">
+    <cfRule type="expression" dxfId="271" priority="650">
       <formula>$B178=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="292" priority="651">
-      <formula>$B178&lt;2</formula>
+    <cfRule type="expression" dxfId="270" priority="652">
+      <formula>$B178=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A106:F108 A109:V111 U113:V119 U120:U121 A124:S125 U124:V125 A135:B140 U135:V140 A141:V141 N142:V142 N143:R143 U143:V148 K144:R144 A148:T148 T152:V157 A158:V161 A162:J163 A164:L168 U166:V168">
-    <cfRule type="expression" dxfId="291" priority="787">
+    <cfRule type="expression" dxfId="269" priority="786">
+      <formula>$B1=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="268" priority="787">
       <formula>$B1&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="290" priority="786">
-      <formula>$B1=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AG4 A5:S6 U5:AG6 A7:AG51 A170:R176">
-    <cfRule type="expression" dxfId="289" priority="489">
+    <cfRule type="expression" dxfId="267" priority="489">
       <formula>$B1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:AG48">
-    <cfRule type="expression" dxfId="288" priority="551">
+    <cfRule type="expression" dxfId="266" priority="551">
       <formula>$B7=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="287" priority="552">
+    <cfRule type="expression" dxfId="265" priority="553">
+      <formula>$B7&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="264" priority="552">
       <formula>$B7=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="286" priority="553">
-      <formula>$B7&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG84 A97:B103 A109:AG120 A121:U121 W121:AG121 A122:AG131 A132:V132 A133:Y133 A134:AG134 S170:AG170 U171:U176 W171:AG176 A177:AG181 A94:AG94">
-    <cfRule type="expression" dxfId="285" priority="750">
+    <cfRule type="expression" dxfId="263" priority="750">
       <formula>$B49=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:AG51 F52:AG52 A52:E54 F53:U54 W53:AG54 A55:AG75 A76:V82 A83:AG84 A94:AG94 A97:B103 A109:AG120 A121:U121 W121:AG121 A122:AG131 A132:V132 A133:Y133 A134:AG134 S170:AG170 U171:U176 W171:AG176 A177:AG181">
-    <cfRule type="expression" dxfId="284" priority="751">
+    <cfRule type="expression" dxfId="262" priority="751">
       <formula>$B49&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:AG96">
-    <cfRule type="expression" dxfId="283" priority="64">
+    <cfRule type="expression" dxfId="261" priority="64">
       <formula>$B83=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85:AG85">
-    <cfRule type="expression" dxfId="282" priority="61">
+    <cfRule type="expression" dxfId="260" priority="63">
+      <formula>$B85&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="259" priority="61">
       <formula>$B85=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="281" priority="62">
+    <cfRule type="expression" dxfId="258" priority="62">
       <formula>$B85=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="280" priority="63">
-      <formula>$B85&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A86:AG93">
-    <cfRule type="expression" dxfId="279" priority="522">
+    <cfRule type="expression" dxfId="257" priority="524">
+      <formula>$B86&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="256" priority="522">
       <formula>$B86=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="278" priority="523">
+    <cfRule type="expression" dxfId="255" priority="523">
       <formula>$B86=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="277" priority="524">
-      <formula>$B86&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A94:AG96 D97:D103 A145:G146 I145:R146 A147:R147">
-    <cfRule type="expression" dxfId="276" priority="733">
+    <cfRule type="expression" dxfId="254" priority="733">
       <formula>$B94=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:AG108">
-    <cfRule type="expression" dxfId="275" priority="506">
-      <formula>$B104=3</formula>
+    <cfRule type="expression" dxfId="253" priority="508">
+      <formula>$B104&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="274" priority="507">
+    <cfRule type="expression" dxfId="252" priority="507">
       <formula>$B104=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="273" priority="508">
-      <formula>$B104&lt;2</formula>
+    <cfRule type="expression" dxfId="251" priority="506">
+      <formula>$B104=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A133:AG134">
-    <cfRule type="expression" dxfId="272" priority="481">
+    <cfRule type="expression" dxfId="250" priority="481">
       <formula>$B133=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A141:AG144 A145:G146 I145:AG146 A147:AG169">
-    <cfRule type="expression" dxfId="271" priority="554">
+    <cfRule type="expression" dxfId="249" priority="554">
       <formula>$B141=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A177:AG181 A55:AG75 A83:AG84 A122:AG131 A132:V132 A133:Y133 A134:AG134 A109:AG120 A76:V82 A97:B103 A49:AG51 F52:AG52 F53:U54 A52:E54 W53:AG54 A121:U121 W121:AG121 S170:AG170 U171:U176 W171:AG176">
-    <cfRule type="expression" dxfId="270" priority="749">
+    <cfRule type="expression" dxfId="248" priority="749">
       <formula>$B49=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C97:C98">
-    <cfRule type="expression" dxfId="269" priority="426">
+    <cfRule type="expression" dxfId="247" priority="426">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="268" priority="427">
+    <cfRule type="expression" dxfId="246" priority="427">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="267" priority="428">
+    <cfRule type="expression" dxfId="245" priority="428">
       <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C97:C100">
-    <cfRule type="expression" dxfId="266" priority="419">
+    <cfRule type="expression" dxfId="244" priority="419">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="265" priority="421">
+    <cfRule type="expression" dxfId="243" priority="420">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="242" priority="421">
       <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="264" priority="420">
-      <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99:C102">
-    <cfRule type="expression" dxfId="263" priority="412">
-      <formula>$B99=3</formula>
+    <cfRule type="expression" dxfId="241" priority="414">
+      <formula>$B99&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="262" priority="413">
+    <cfRule type="expression" dxfId="240" priority="413">
       <formula>$B99=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="261" priority="414">
-      <formula>$B99&lt;2</formula>
+    <cfRule type="expression" dxfId="239" priority="412">
+      <formula>$B99=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101:C103">
-    <cfRule type="expression" dxfId="260" priority="407">
+    <cfRule type="expression" dxfId="238" priority="405">
+      <formula>$B101=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="237" priority="407">
       <formula>$B101&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="259" priority="406">
+    <cfRule type="expression" dxfId="236" priority="406">
       <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="258" priority="405">
-      <formula>$B101=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102:C103">
-    <cfRule type="expression" dxfId="257" priority="51">
-      <formula>$B102=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="256" priority="53">
+    <cfRule type="expression" dxfId="235" priority="53">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="255" priority="52">
+    <cfRule type="expression" dxfId="234" priority="52">
       <formula>$B102=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="233" priority="51">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C135:T135 C136:R140">
-    <cfRule type="expression" dxfId="254" priority="611">
+    <cfRule type="expression" dxfId="232" priority="609">
+      <formula>$B135=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="231" priority="611">
       <formula>$B135=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="253" priority="608">
+    <cfRule type="expression" dxfId="230" priority="610">
+      <formula>$B135&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="229" priority="608">
       <formula>$B135=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="252" priority="609">
-      <formula>$B135=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="251" priority="610">
-      <formula>$B135&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D80 D82 D84:D134 D141:D181">
@@ -20057,878 +19905,858 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D97:E103">
-    <cfRule type="expression" dxfId="250" priority="400">
+    <cfRule type="expression" dxfId="228" priority="400">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="249" priority="398">
+    <cfRule type="expression" dxfId="227" priority="399">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="226" priority="398">
       <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="248" priority="399">
-      <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E97:E103">
-    <cfRule type="expression" dxfId="247" priority="397">
+    <cfRule type="expression" dxfId="225" priority="395">
+      <formula>$B97=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="224" priority="397">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="246" priority="395">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="245" priority="396">
+    <cfRule type="expression" dxfId="223" priority="396">
       <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E83:Q83 Q124:Q125">
-    <cfRule type="expression" dxfId="244" priority="627">
+    <cfRule type="expression" dxfId="222" priority="627">
       <formula>_xlfn.ISFORMULA(E83)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E135:Q140">
-    <cfRule type="expression" dxfId="243" priority="607">
+    <cfRule type="expression" dxfId="221" priority="607">
       <formula>_xlfn.ISFORMULA(E135)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F102:F103 F97:I99 F100 H100:I100 F101:I101 H102:I102">
+    <cfRule type="expression" dxfId="220" priority="187">
+      <formula>$B97=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F103">
+    <cfRule type="expression" dxfId="219" priority="20">
+      <formula>$B103=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="218" priority="21">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="217" priority="22">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F109:F111">
-    <cfRule type="expression" dxfId="242" priority="74">
+    <cfRule type="expression" dxfId="216" priority="74">
       <formula>$B109=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111">
-    <cfRule type="expression" dxfId="241" priority="70">
+    <cfRule type="expression" dxfId="215" priority="69">
+      <formula>$B111=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="214" priority="70">
       <formula>$B111&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="240" priority="69">
-      <formula>$B111=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="239" priority="68">
+    <cfRule type="expression" dxfId="213" priority="68">
       <formula>$B111=3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F102:G102">
+    <cfRule type="expression" dxfId="212" priority="25">
+      <formula>$B102&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="211" priority="24">
+      <formula>$B102=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="210" priority="23">
+      <formula>$B102=3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F109:G110">
-    <cfRule type="expression" dxfId="238" priority="73">
+    <cfRule type="expression" dxfId="209" priority="72">
+      <formula>$B109=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="208" priority="73">
       <formula>$B109&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="237" priority="72">
-      <formula>$B109=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="236" priority="71">
+    <cfRule type="expression" dxfId="207" priority="71">
       <formula>$B109=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51:I54">
-    <cfRule type="expression" dxfId="235" priority="556">
+    <cfRule type="expression" dxfId="206" priority="556">
       <formula>$B51=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="234" priority="557">
+    <cfRule type="expression" dxfId="205" priority="557">
       <formula>$B51=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="233" priority="558">
+    <cfRule type="expression" dxfId="204" priority="559">
+      <formula>$B51=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="203" priority="558">
       <formula>$B51&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="232" priority="559">
-      <formula>$B51=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:I98">
-    <cfRule type="expression" dxfId="231" priority="377">
+    <cfRule type="expression" dxfId="202" priority="379">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="201" priority="377">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="230" priority="378">
+    <cfRule type="expression" dxfId="200" priority="378">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="229" priority="379">
-      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:I99 F100 H100:I100 F101:I101 H102:I102 F102:F103">
-    <cfRule type="expression" dxfId="228" priority="189">
+    <cfRule type="expression" dxfId="199" priority="189">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="227" priority="188">
+    <cfRule type="expression" dxfId="198" priority="188">
       <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="226" priority="187">
-      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:I101">
-    <cfRule type="expression" dxfId="225" priority="57">
-      <formula>$B99=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="224" priority="59">
+    <cfRule type="expression" dxfId="197" priority="59">
       <formula>$B99&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="223" priority="58">
+    <cfRule type="expression" dxfId="196" priority="58">
       <formula>$B99=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="195" priority="57">
+      <formula>$B99=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F102:I103">
-    <cfRule type="expression" dxfId="222" priority="34">
+    <cfRule type="expression" dxfId="194" priority="34">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="221" priority="33">
+    <cfRule type="expression" dxfId="193" priority="33">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="220" priority="32">
+    <cfRule type="expression" dxfId="192" priority="32">
       <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:I103">
-    <cfRule type="expression" dxfId="219" priority="180">
+    <cfRule type="expression" dxfId="191" priority="181">
+      <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="190" priority="180">
       <formula>$B103=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="218" priority="181">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="217" priority="182">
+    <cfRule type="expression" dxfId="189" priority="182">
       <formula>$B103&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:U54 W53:AG54 A55:AG75 A104:AG105 A106:V109 A109:AG120 A121:U121 W121:AG121 A122:AG131 A126:V141 S170:AG170 U171:U176 W171:AG176 A177:AG181">
-    <cfRule type="expression" dxfId="216" priority="752">
+    <cfRule type="expression" dxfId="188" priority="752">
       <formula>$B53=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:AG52 A52:E54">
-    <cfRule type="expression" dxfId="215" priority="550">
+    <cfRule type="expression" dxfId="187" priority="550">
       <formula>$B52=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G100">
-    <cfRule type="expression" dxfId="214" priority="56">
-      <formula>$B100&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="213" priority="55">
+    <cfRule type="expression" dxfId="186" priority="55">
       <formula>$B100=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="212" priority="54">
+    <cfRule type="expression" dxfId="185" priority="54">
       <formula>$B100=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G102">
-    <cfRule type="expression" dxfId="211" priority="31">
-      <formula>$B102&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="210" priority="30">
-      <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="209" priority="29">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="184" priority="56">
+      <formula>$B100&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G106:I107">
-    <cfRule type="expression" dxfId="208" priority="783">
+    <cfRule type="expression" dxfId="183" priority="781">
+      <formula>$B106=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="182" priority="782">
+      <formula>$B106=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="181" priority="783">
       <formula>$B106&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="207" priority="782">
-      <formula>$B106=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="206" priority="781">
-      <formula>$B106=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="205" priority="784">
+    <cfRule type="expression" dxfId="180" priority="784">
       <formula>$B106=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H145:H146 K162:L163">
-    <cfRule type="expression" dxfId="204" priority="666">
-      <formula>$B146=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="203" priority="667">
+    <cfRule type="expression" dxfId="179" priority="667">
       <formula>$B146&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="668">
+    <cfRule type="expression" dxfId="178" priority="668">
       <formula>$B146=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="177" priority="666">
+      <formula>$B146=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H145:H146">
-    <cfRule type="expression" dxfId="201" priority="1057">
-      <formula>$B146&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="200" priority="1059">
+    <cfRule type="expression" dxfId="176" priority="1059">
       <formula>$B146=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="199" priority="1056">
+    <cfRule type="expression" dxfId="175" priority="1056">
       <formula>$B146=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="174" priority="1057">
+      <formula>$B146&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5">
-    <cfRule type="expression" dxfId="198" priority="588">
+    <cfRule type="expression" dxfId="173" priority="587">
+      <formula>$B5=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="172" priority="588">
       <formula>$B5=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="590">
-      <formula>$B5=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="196" priority="589">
+    <cfRule type="expression" dxfId="171" priority="589">
       <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="195" priority="587">
-      <formula>$B5=3</formula>
+    <cfRule type="expression" dxfId="170" priority="590">
+      <formula>$B5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J71:L73">
-    <cfRule type="expression" dxfId="194" priority="642">
+    <cfRule type="expression" dxfId="169" priority="638">
+      <formula>_xlfn.ISFORMULA(J71)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="168" priority="642">
       <formula>$B71=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="193" priority="638">
-      <formula>_xlfn.ISFORMULA(J71)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:Q96 J104:Q1048576">
-    <cfRule type="expression" dxfId="192" priority="648">
+    <cfRule type="expression" dxfId="167" priority="648">
       <formula>_xlfn.ISFORMULA(J1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:Q70">
-    <cfRule type="expression" dxfId="191" priority="643">
+    <cfRule type="expression" dxfId="166" priority="643">
       <formula>_xlfn.ISFORMULA(J68)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69:S73">
-    <cfRule type="expression" dxfId="190" priority="636">
-      <formula>$B69&lt;2</formula>
+    <cfRule type="expression" dxfId="165" priority="634">
+      <formula>$B69=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="635">
+    <cfRule type="expression" dxfId="164" priority="635">
       <formula>$B69=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="634">
-      <formula>$B69=3</formula>
+    <cfRule type="expression" dxfId="163" priority="636">
+      <formula>$B69&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 J69:S70 U69:V73">
-    <cfRule type="expression" dxfId="187" priority="647">
+    <cfRule type="expression" dxfId="162" priority="647">
       <formula>$B68=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:V68 U69:V73">
-    <cfRule type="expression" dxfId="186" priority="646">
-      <formula>$B68&lt;2</formula>
+    <cfRule type="expression" dxfId="161" priority="644">
+      <formula>$B68=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="645">
+    <cfRule type="expression" dxfId="160" priority="645">
       <formula>$B68=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="184" priority="644">
-      <formula>$B68=3</formula>
+    <cfRule type="expression" dxfId="159" priority="646">
+      <formula>$B68&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
-    <cfRule type="expression" dxfId="183" priority="580">
+    <cfRule type="expression" dxfId="158" priority="580">
       <formula>_xlfn.ISFORMULA(K81)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K103:L103">
-    <cfRule type="expression" dxfId="182" priority="145">
-      <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="181" priority="146">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="180" priority="147">
-      <formula>$B103&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K162:L163 H145:H146">
-    <cfRule type="expression" dxfId="179" priority="665">
+    <cfRule type="expression" dxfId="157" priority="665">
       <formula>$B146=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M98">
-    <cfRule type="expression" dxfId="178" priority="331">
+    <cfRule type="expression" dxfId="156" priority="331">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="332">
+    <cfRule type="expression" dxfId="155" priority="332">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="333">
+    <cfRule type="expression" dxfId="154" priority="333">
       <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M101">
-    <cfRule type="expression" dxfId="175" priority="159">
+    <cfRule type="expression" dxfId="153" priority="159">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="157">
+    <cfRule type="expression" dxfId="152" priority="158">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="151" priority="157">
       <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="173" priority="158">
-      <formula>$B97=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:M103">
-    <cfRule type="expression" dxfId="172" priority="148">
+    <cfRule type="expression" dxfId="150" priority="152">
+      <formula>$B97=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="148">
       <formula>_xlfn.ISFORMULA(K97)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="171" priority="152">
-      <formula>$B97=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:M103">
-    <cfRule type="expression" dxfId="170" priority="149">
-      <formula>$B99=3</formula>
+    <cfRule type="expression" dxfId="148" priority="151">
+      <formula>$B99&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="150">
+    <cfRule type="expression" dxfId="147" priority="150">
       <formula>$B99=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="151">
-      <formula>$B99&lt;2</formula>
+    <cfRule type="expression" dxfId="146" priority="149">
+      <formula>$B99=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K102:M102">
-    <cfRule type="expression" dxfId="167" priority="50">
+    <cfRule type="expression" dxfId="145" priority="50">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="49">
+    <cfRule type="expression" dxfId="144" priority="48">
+      <formula>$B102=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="143" priority="49">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="48">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K103:M103">
+    <cfRule type="expression" dxfId="142" priority="1">
+      <formula>$B103=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="141" priority="3">
+      <formula>$B103&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="140" priority="2">
+      <formula>$B103=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K142:M143">
+    <cfRule type="expression" dxfId="139" priority="748">
+      <formula>$B142=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="138" priority="747">
+      <formula>$B142&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="137" priority="746">
+      <formula>$B142=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="136" priority="745">
+      <formula>$B142=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L112">
+    <cfRule type="expression" dxfId="135" priority="984">
+      <formula>#REF!=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="134" priority="985">
+      <formula>#REF!&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="133" priority="594">
+      <formula>$B112=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="132" priority="986">
+      <formula>#REF!=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="987">
+      <formula>#REF!=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L112:V112">
+    <cfRule type="expression" dxfId="130" priority="593">
+      <formula>$B112&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="129" priority="591">
+      <formula>$B112=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="128" priority="592">
+      <formula>$B112=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M102:M103">
+    <cfRule type="expression" dxfId="127" priority="18">
+      <formula>$B102=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="126" priority="19">
+      <formula>$B102&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="125" priority="17">
       <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K142:M143">
-    <cfRule type="expression" dxfId="164" priority="745">
-      <formula>$B142=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="163" priority="748">
-      <formula>$B142=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="162" priority="747">
-      <formula>$B142&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="746">
-      <formula>$B142=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L112">
-    <cfRule type="expression" dxfId="160" priority="987">
-      <formula>#REF!=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="159" priority="984">
-      <formula>#REF!=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="985">
-      <formula>#REF!&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="594">
-      <formula>$B112=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="156" priority="986">
-      <formula>#REF!=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L112:V112">
-    <cfRule type="expression" dxfId="155" priority="591">
-      <formula>$B112=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="154" priority="592">
-      <formula>$B112=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="153" priority="593">
-      <formula>$B112&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N81">
-    <cfRule type="expression" dxfId="149" priority="575">
+    <cfRule type="expression" dxfId="124" priority="575">
       <formula>_xlfn.ISFORMULA(N81)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O97:O98">
-    <cfRule type="expression" dxfId="148" priority="317">
+    <cfRule type="expression" dxfId="123" priority="316">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="122" priority="317">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="147" priority="316">
-      <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="315">
+    <cfRule type="expression" dxfId="121" priority="315">
       <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O97:O103">
-    <cfRule type="expression" dxfId="145" priority="306">
+    <cfRule type="expression" dxfId="120" priority="309">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="119" priority="308">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="307">
+      <formula>$B97=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="117" priority="306">
       <formula>_xlfn.ISFORMULA(O97)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="307">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="308">
-      <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="142" priority="309">
-      <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="310">
+    <cfRule type="expression" dxfId="116" priority="310">
       <formula>$B97=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O99:O103">
-    <cfRule type="expression" dxfId="140" priority="305">
+    <cfRule type="expression" dxfId="115" priority="305">
       <formula>$B99&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="139" priority="304">
+    <cfRule type="expression" dxfId="114" priority="303">
+      <formula>$B99=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="304">
       <formula>$B99=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="138" priority="303">
-      <formula>$B99=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71:Q73">
-    <cfRule type="expression" dxfId="137" priority="633">
+    <cfRule type="expression" dxfId="112" priority="633">
       <formula>_xlfn.ISFORMULA(Q71)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:Q103">
-    <cfRule type="expression" dxfId="136" priority="132">
+    <cfRule type="expression" dxfId="111" priority="132">
       <formula>_xlfn.ISFORMULA(Q97)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q149">
-    <cfRule type="expression" dxfId="135" priority="803">
+    <cfRule type="expression" dxfId="110" priority="802">
+      <formula>$B150=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="109" priority="803">
       <formula>$B150=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="802">
-      <formula>$B150=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="133" priority="804">
+    <cfRule type="expression" dxfId="108" priority="804">
       <formula>$B150&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="805">
+    <cfRule type="expression" dxfId="107" priority="805">
       <formula>$B150=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:R98">
-    <cfRule type="expression" dxfId="131" priority="284">
+    <cfRule type="expression" dxfId="106" priority="285">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="284">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="283">
+    <cfRule type="expression" dxfId="104" priority="283">
       <formula>$B97=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="285">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q97:R100">
+    <cfRule type="expression" dxfId="103" priority="276">
+      <formula>$B97=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="277">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="278">
       <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q97:R100">
-    <cfRule type="expression" dxfId="128" priority="278">
-      <formula>$B97&lt;2</formula>
+  <conditionalFormatting sqref="Q101:R101">
+    <cfRule type="expression" dxfId="100" priority="125">
+      <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="276">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="126" priority="277">
-      <formula>$B97=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q101:R101">
-    <cfRule type="expression" dxfId="125" priority="127">
-      <formula>$B101&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="126">
+    <cfRule type="expression" dxfId="99" priority="126">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="125">
-      <formula>$B101=3</formula>
+    <cfRule type="expression" dxfId="98" priority="127">
+      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q102:R102">
-    <cfRule type="expression" dxfId="122" priority="47">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="97" priority="45">
+      <formula>$B102=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="46">
+    <cfRule type="expression" dxfId="96" priority="46">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="45">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="95" priority="47">
+      <formula>$B102&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q103:R103">
-    <cfRule type="expression" dxfId="119" priority="119">
+    <cfRule type="expression" dxfId="94" priority="119">
       <formula>$B103=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="120">
+    <cfRule type="expression" dxfId="93" priority="120">
       <formula>$B103&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="118">
+    <cfRule type="expression" dxfId="92" priority="118">
       <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q71:S73">
-    <cfRule type="expression" dxfId="116" priority="637">
+    <cfRule type="expression" dxfId="91" priority="637">
       <formula>$B71=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q99:S100">
-    <cfRule type="expression" dxfId="115" priority="269">
+    <cfRule type="expression" dxfId="90" priority="269">
       <formula>$B99=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="270">
+    <cfRule type="expression" dxfId="89" priority="270">
       <formula>$B99=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="271">
+    <cfRule type="expression" dxfId="88" priority="271">
       <formula>$B99&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:S101">
-    <cfRule type="expression" dxfId="112" priority="104">
+    <cfRule type="expression" dxfId="87" priority="106">
+      <formula>$B101&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="104">
       <formula>$B101=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="111" priority="105">
+    <cfRule type="expression" dxfId="85" priority="105">
       <formula>$B101=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="110" priority="106">
-      <formula>$B101&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q102:S102">
-    <cfRule type="expression" dxfId="109" priority="42">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="84" priority="44">
+      <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="43">
+    <cfRule type="expression" dxfId="83" priority="43">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="44">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="82" priority="42">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q103:S103">
-    <cfRule type="expression" dxfId="106" priority="113">
+    <cfRule type="expression" dxfId="81" priority="113">
       <formula>$B103&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="112">
+    <cfRule type="expression" dxfId="80" priority="111">
+      <formula>$B103=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="112">
       <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="111">
-      <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97:T103">
-    <cfRule type="expression" dxfId="103" priority="93">
+    <cfRule type="expression" dxfId="78" priority="93">
       <formula>$B97=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:S100">
-    <cfRule type="expression" dxfId="102" priority="263">
+    <cfRule type="expression" dxfId="77" priority="264">
+      <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="263">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="264">
-      <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="262">
+    <cfRule type="expression" dxfId="75" priority="262">
       <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S102">
-    <cfRule type="expression" dxfId="99" priority="39">
+    <cfRule type="expression" dxfId="74" priority="39">
       <formula>$B102=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="41">
+    <cfRule type="expression" dxfId="73" priority="41">
       <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="40">
+    <cfRule type="expression" dxfId="72" priority="40">
       <formula>$B102=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S152">
-    <cfRule type="expression" dxfId="96" priority="732">
+    <cfRule type="expression" dxfId="71" priority="731">
+      <formula>$B152&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="732">
       <formula>$B152=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="730">
-      <formula>$B152=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="729">
+    <cfRule type="expression" dxfId="69" priority="729">
       <formula>$B152=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="731">
-      <formula>$B152&lt;2</formula>
+    <cfRule type="expression" dxfId="68" priority="730">
+      <formula>$B152=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S156:S157">
-    <cfRule type="expression" dxfId="92" priority="725">
+    <cfRule type="expression" dxfId="67" priority="725">
       <formula>$B156=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="728">
+    <cfRule type="expression" dxfId="66" priority="726">
+      <formula>$B156=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="728">
       <formula>$B156=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="727">
+    <cfRule type="expression" dxfId="64" priority="727">
       <formula>$B156&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="726">
-      <formula>$B156=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:T98">
-    <cfRule type="expression" dxfId="88" priority="255">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="256">
+    <cfRule type="expression" dxfId="63" priority="256">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="257">
+    <cfRule type="expression" dxfId="62" priority="257">
       <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="255">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S101:T101">
-    <cfRule type="expression" dxfId="85" priority="94">
-      <formula>$B101=3</formula>
+    <cfRule type="expression" dxfId="60" priority="96">
+      <formula>$B101&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="95">
+    <cfRule type="expression" dxfId="59" priority="95">
       <formula>$B101=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="96">
-      <formula>$B101&lt;2</formula>
+    <cfRule type="expression" dxfId="58" priority="94">
+      <formula>$B101=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S103:T103">
-    <cfRule type="expression" dxfId="82" priority="90">
-      <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="92">
+    <cfRule type="expression" dxfId="57" priority="92">
       <formula>$B103&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="91">
+    <cfRule type="expression" dxfId="56" priority="91">
       <formula>$B103=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="90">
+      <formula>$B103=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S90:V93">
-    <cfRule type="expression" dxfId="79" priority="626">
+    <cfRule type="expression" dxfId="54" priority="626">
       <formula>$B90=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S150:V151">
-    <cfRule type="expression" dxfId="78" priority="692">
-      <formula>$B150=0</formula>
+    <cfRule type="expression" dxfId="53" priority="689">
+      <formula>$B150=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="690">
+    <cfRule type="expression" dxfId="52" priority="690">
       <formula>$B150=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="689">
-      <formula>$B150=3</formula>
+    <cfRule type="expression" dxfId="51" priority="691">
+      <formula>$B150&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="691">
-      <formula>$B150&lt;2</formula>
+    <cfRule type="expression" dxfId="50" priority="692">
+      <formula>$B150=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5">
-    <cfRule type="expression" dxfId="74" priority="485">
+    <cfRule type="expression" dxfId="49" priority="484">
+      <formula>$B5=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="485">
       <formula>$B5&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="484">
-      <formula>$B5=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="483">
+    <cfRule type="expression" dxfId="47" priority="483">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="482">
+    <cfRule type="expression" dxfId="46" priority="482">
       <formula>$B5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6">
-    <cfRule type="expression" dxfId="70" priority="1045">
+    <cfRule type="expression" dxfId="45" priority="1040">
+      <formula>$B5=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="1045">
       <formula>$B5=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="1040">
-      <formula>$B5=2</formula>
+    <cfRule type="expression" dxfId="43" priority="1043">
+      <formula>$B5=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="1041">
+    <cfRule type="expression" dxfId="42" priority="1041">
       <formula>$B5&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="1043">
-      <formula>$B5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T97:T100">
-    <cfRule type="expression" dxfId="66" priority="248">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="249">
+    <cfRule type="expression" dxfId="41" priority="249">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="250">
+    <cfRule type="expression" dxfId="40" priority="250">
       <formula>$B97&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="248">
+      <formula>$B97=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T99:T102">
-    <cfRule type="expression" dxfId="63" priority="97">
+    <cfRule type="expression" dxfId="38" priority="98">
+      <formula>$B99=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="97">
       <formula>$B99=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="98">
-      <formula>$B99=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="99">
+    <cfRule type="expression" dxfId="36" priority="99">
       <formula>$B99&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T100">
-    <cfRule type="expression" dxfId="60" priority="26">
-      <formula>$B100=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="28">
+    <cfRule type="expression" dxfId="35" priority="28">
       <formula>$B100&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="27">
+    <cfRule type="expression" dxfId="34" priority="27">
       <formula>$B100=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="26">
+      <formula>$B100=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T102:T103">
-    <cfRule type="expression" dxfId="57" priority="36">
-      <formula>$B102=3</formula>
+    <cfRule type="expression" dxfId="32" priority="38">
+      <formula>$B102&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="37">
+    <cfRule type="expression" dxfId="31" priority="37">
       <formula>$B102=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="38">
-      <formula>$B102&lt;2</formula>
+    <cfRule type="expression" dxfId="30" priority="36">
+      <formula>$B102=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U106">
-    <cfRule type="expression" dxfId="54" priority="813">
+    <cfRule type="expression" dxfId="29" priority="813">
       <formula>$B105=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="812">
+    <cfRule type="expression" dxfId="28" priority="812">
       <formula>$B105&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="811">
+    <cfRule type="expression" dxfId="27" priority="811">
       <formula>$B105=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="810">
+    <cfRule type="expression" dxfId="26" priority="810">
       <formula>$B105=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U135:AG140">
-    <cfRule type="expression" dxfId="50" priority="433">
+    <cfRule type="expression" dxfId="25" priority="433">
       <formula>$B135=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W97:W103">
-    <cfRule type="expression" dxfId="49" priority="239">
+    <cfRule type="expression" dxfId="24" priority="237">
+      <formula>$B97=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="238">
+      <formula>$B97=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="239">
       <formula>$B97&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="237">
-      <formula>$B97=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="238">
-      <formula>$B97=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="240">
+    <cfRule type="expression" dxfId="21" priority="240">
       <formula>$B97=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W76:AG82">
-    <cfRule type="expression" dxfId="45" priority="533">
+    <cfRule type="expression" dxfId="20" priority="531">
+      <formula>$B76=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="532">
+      <formula>$B76&lt;2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="533">
       <formula>$B76=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="532">
-      <formula>$B76&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="531">
-      <formula>$B76=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="530">
+    <cfRule type="expression" dxfId="17" priority="530">
       <formula>$B76=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W95:AG96 A145:G146 I145:R146 A147:R147">
-    <cfRule type="expression" dxfId="41" priority="735">
+    <cfRule type="expression" dxfId="16" priority="734">
+      <formula>$B95=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="735">
       <formula>$B95&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="734">
-      <formula>$B95=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W106:AG108">
-    <cfRule type="expression" dxfId="39" priority="509">
+    <cfRule type="expression" dxfId="14" priority="509">
       <formula>$B106=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W132:AG132">
-    <cfRule type="expression" dxfId="38" priority="502">
+    <cfRule type="expression" dxfId="13" priority="503">
+      <formula>$B132=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="505">
+      <formula>$B132=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="502">
       <formula>$B132=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="503">
-      <formula>$B132=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="504">
+    <cfRule type="expression" dxfId="10" priority="504">
       <formula>$B132&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="505">
-      <formula>$B132=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W135:AG140">
-    <cfRule type="expression" dxfId="34" priority="430">
+    <cfRule type="expression" dxfId="9" priority="430">
       <formula>$B135=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="431">
+    <cfRule type="expression" dxfId="8" priority="431">
       <formula>$B135=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="432">
+    <cfRule type="expression" dxfId="7" priority="432">
       <formula>$B135&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z97:AG103">
-    <cfRule type="expression" dxfId="31" priority="82">
+    <cfRule type="expression" dxfId="6" priority="82">
       <formula>$B97=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="81">
-      <formula>$B97&lt;2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="80">
+    <cfRule type="expression" dxfId="5" priority="80">
       <formula>$B97=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="79">
+    <cfRule type="expression" dxfId="4" priority="79">
       <formula>$B97=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="81">
+      <formula>$B97&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z133:AG133">
-    <cfRule type="expression" dxfId="27" priority="478">
-      <formula>$B133=3</formula>
+    <cfRule type="expression" dxfId="2" priority="480">
+      <formula>$B133&lt;2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="479">
+    <cfRule type="expression" dxfId="1" priority="479">
       <formula>$B133=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="480">
-      <formula>$B133&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F102">
-    <cfRule type="expression" dxfId="24" priority="23">
-      <formula>$B102=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="24">
-      <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="25">
-      <formula>$B102&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F103">
-    <cfRule type="expression" dxfId="21" priority="20">
-      <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="21">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="22">
-      <formula>$B103&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M102:M103">
-    <cfRule type="expression" dxfId="17" priority="17">
-      <formula>$B102=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18">
-      <formula>$B102=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="19">
-      <formula>$B102&lt;2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M103">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$B103=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$B103=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$B103&lt;2</formula>
+    <cfRule type="expression" dxfId="0" priority="478">
+      <formula>$B133=3</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="15">
@@ -24299,7 +24127,7 @@
       <c r="T3" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="U3" s="163" t="s">
+      <c r="U3" s="164" t="s">
         <v>42</v>
       </c>
       <c r="V3" s="108"/>
@@ -24495,7 +24323,7 @@
       <c r="T5" s="160" t="s">
         <v>63</v>
       </c>
-      <c r="U5" s="163" t="s">
+      <c r="U5" s="164" t="s">
         <v>58</v>
       </c>
       <c r="V5" s="108"/>
@@ -24945,7 +24773,7 @@
       <c r="T11" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U11" s="162" t="s">
+      <c r="U11" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V11" s="108"/>
@@ -25498,7 +25326,7 @@
       <c r="T18" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U18" s="162" t="s">
+      <c r="U18" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V18" s="108"/>
@@ -25909,7 +25737,7 @@
       <c r="T23" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U23" s="162" t="s">
+      <c r="U23" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V23" s="108"/>
@@ -26320,7 +26148,7 @@
       <c r="T28" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U28" s="162" t="s">
+      <c r="U28" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V28" s="108"/>
@@ -26731,7 +26559,7 @@
       <c r="T33" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U33" s="162" t="s">
+      <c r="U33" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V33" s="108"/>
@@ -27142,7 +26970,7 @@
       <c r="T38" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U38" s="162" t="s">
+      <c r="U38" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V38" s="108"/>
@@ -27692,7 +27520,7 @@
       <c r="T45" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U45" s="162" t="s">
+      <c r="U45" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V45" s="108"/>
@@ -28250,7 +28078,7 @@
       <c r="T52" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U52" s="162" t="s">
+      <c r="U52" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V52" s="108"/>
@@ -28666,7 +28494,7 @@
       <c r="T57" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U57" s="162" t="s">
+      <c r="U57" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V57" s="108"/>
@@ -29084,7 +28912,7 @@
       <c r="T62" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U62" s="162" t="s">
+      <c r="U62" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V62" s="108"/>
@@ -29495,7 +29323,7 @@
       <c r="T67" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U67" s="162" t="s">
+      <c r="U67" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V67" s="108"/>
@@ -30045,7 +29873,7 @@
       <c r="T74" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U74" s="162" t="s">
+      <c r="U74" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V74" s="108"/>
@@ -30456,7 +30284,7 @@
       <c r="T79" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U79" s="162" t="s">
+      <c r="U79" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V79" s="108"/>
@@ -31019,7 +30847,7 @@
       <c r="T86" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U86" s="162" t="s">
+      <c r="U86" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V86" s="108"/>
@@ -31578,7 +31406,7 @@
       <c r="T93" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U93" s="162" t="s">
+      <c r="U93" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V93" s="108"/>
@@ -31989,7 +31817,7 @@
       <c r="T98" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U98" s="162" t="s">
+      <c r="U98" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V98" s="108"/>
@@ -32560,7 +32388,7 @@
       <c r="T105" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U105" s="162" t="s">
+      <c r="U105" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V105" s="108"/>
@@ -33131,7 +32959,7 @@
       <c r="T112" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U112" s="162" t="s">
+      <c r="U112" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V112" s="108"/>
@@ -33555,7 +33383,7 @@
       <c r="T117" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U117" s="162" t="s">
+      <c r="U117" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V117" s="108"/>
@@ -33994,7 +33822,7 @@
       <c r="T122" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U122" s="162" t="s">
+      <c r="U122" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V122" s="108"/>
@@ -34405,7 +34233,7 @@
       <c r="T127" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="U127" s="162" t="s">
+      <c r="U127" s="163" t="s">
         <v>76</v>
       </c>
       <c r="V127" s="108"/>
@@ -41822,10 +41650,10 @@
       <c r="R225" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="S225" s="164" t="s">
+      <c r="S225" s="162" t="s">
         <v>340</v>
       </c>
-      <c r="T225" s="164" t="s">
+      <c r="T225" s="162" t="s">
         <v>341</v>
       </c>
       <c r="U225" s="108"/>
@@ -44594,21 +44422,45 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="S23:S25"/>
-    <mergeCell ref="S225:S230"/>
-    <mergeCell ref="S122:S124"/>
-    <mergeCell ref="U57:U59"/>
-    <mergeCell ref="S38:S40"/>
-    <mergeCell ref="U62:U64"/>
-    <mergeCell ref="T117:T119"/>
-    <mergeCell ref="S112:S114"/>
-    <mergeCell ref="S57:S59"/>
-    <mergeCell ref="S28:S30"/>
-    <mergeCell ref="U28:U30"/>
-    <mergeCell ref="U93:U95"/>
-    <mergeCell ref="S127:S129"/>
-    <mergeCell ref="T225:T230"/>
-    <mergeCell ref="S74:S76"/>
+    <mergeCell ref="S242:S245"/>
+    <mergeCell ref="U33:U35"/>
+    <mergeCell ref="U98:U100"/>
+    <mergeCell ref="U67:U69"/>
+    <mergeCell ref="U117:U119"/>
+    <mergeCell ref="U52:U54"/>
+    <mergeCell ref="U79:U81"/>
+    <mergeCell ref="U38:U40"/>
+    <mergeCell ref="U112:U114"/>
+    <mergeCell ref="T122:T124"/>
+    <mergeCell ref="S67:S69"/>
+    <mergeCell ref="T67:T69"/>
+    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S18:S20"/>
+    <mergeCell ref="U122:U124"/>
+    <mergeCell ref="U18:U20"/>
+    <mergeCell ref="T79:T81"/>
+    <mergeCell ref="U127:U129"/>
+    <mergeCell ref="U23:U25"/>
+    <mergeCell ref="T105:T107"/>
+    <mergeCell ref="T52:T54"/>
+    <mergeCell ref="T86:T88"/>
+    <mergeCell ref="S93:S95"/>
+    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="S33:S35"/>
+    <mergeCell ref="T23:T25"/>
+    <mergeCell ref="T28:T30"/>
+    <mergeCell ref="S45:S47"/>
+    <mergeCell ref="S79:S81"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="T57:T59"/>
+    <mergeCell ref="T33:T35"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="T98:T100"/>
+    <mergeCell ref="T45:T47"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="T11:T13"/>
     <mergeCell ref="S11:S13"/>
     <mergeCell ref="T74:T76"/>
     <mergeCell ref="T112:T114"/>
@@ -44625,45 +44477,21 @@
     <mergeCell ref="S52:S54"/>
     <mergeCell ref="S86:S88"/>
     <mergeCell ref="U86:U88"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="T57:T59"/>
-    <mergeCell ref="T33:T35"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="T98:T100"/>
-    <mergeCell ref="T45:T47"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T11:T13"/>
-    <mergeCell ref="S18:S20"/>
-    <mergeCell ref="U122:U124"/>
-    <mergeCell ref="U18:U20"/>
-    <mergeCell ref="T79:T81"/>
-    <mergeCell ref="U127:U129"/>
-    <mergeCell ref="U23:U25"/>
-    <mergeCell ref="T105:T107"/>
-    <mergeCell ref="T52:T54"/>
-    <mergeCell ref="T86:T88"/>
-    <mergeCell ref="S93:S95"/>
-    <mergeCell ref="S62:S64"/>
-    <mergeCell ref="S33:S35"/>
-    <mergeCell ref="T23:T25"/>
-    <mergeCell ref="T28:T30"/>
-    <mergeCell ref="S45:S47"/>
-    <mergeCell ref="S79:S81"/>
-    <mergeCell ref="S242:S245"/>
-    <mergeCell ref="U33:U35"/>
-    <mergeCell ref="U98:U100"/>
-    <mergeCell ref="U67:U69"/>
-    <mergeCell ref="U117:U119"/>
-    <mergeCell ref="U52:U54"/>
-    <mergeCell ref="U79:U81"/>
-    <mergeCell ref="U38:U40"/>
-    <mergeCell ref="U112:U114"/>
-    <mergeCell ref="T122:T124"/>
-    <mergeCell ref="S67:S69"/>
-    <mergeCell ref="T67:T69"/>
-    <mergeCell ref="T127:T129"/>
+    <mergeCell ref="S23:S25"/>
+    <mergeCell ref="S225:S230"/>
+    <mergeCell ref="S122:S124"/>
+    <mergeCell ref="U57:U59"/>
+    <mergeCell ref="S38:S40"/>
+    <mergeCell ref="U62:U64"/>
+    <mergeCell ref="T117:T119"/>
+    <mergeCell ref="S112:S114"/>
+    <mergeCell ref="S57:S59"/>
+    <mergeCell ref="S28:S30"/>
+    <mergeCell ref="U28:U30"/>
+    <mergeCell ref="U93:U95"/>
+    <mergeCell ref="S127:S129"/>
+    <mergeCell ref="T225:T230"/>
+    <mergeCell ref="S74:S76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
